--- a/etf_holdings/2026-09-29_daily_changes_changed_only.xlsx
+++ b/etf_holdings/2026-09-29_daily_changes_changed_only.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M93"/>
+  <dimension ref="A1:M69"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1494,7 +1494,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>00982A</t>
+          <t>00403A</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1509,55 +1509,55 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>2059</t>
+          <t>2345</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>川湖</t>
+          <t>智邦</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>川湖</t>
+          <t>智邦</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>4.39%</t>
+          <t>2.42%</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>4.37%</t>
+          <t>2.24%</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>-0.02%</t>
+          <t>-0.18%</t>
         </is>
       </c>
       <c r="J18" t="n">
-        <v>180000</v>
+        <v>1900000</v>
       </c>
       <c r="K18" t="n">
-        <v>179000</v>
+        <v>1800000</v>
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>-1,000</t>
+          <t>-100,000</t>
         </is>
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>2026-09-27_00982A_full_holdings.xlsx</t>
+          <t>2026-09-27_00403A_full_holdings.xlsx</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>00982A</t>
+          <t>00403A</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1572,55 +1572,55 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>2301</t>
+          <t>2360</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>光寶科</t>
+          <t>致茂</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>光寶科</t>
+          <t>致茂</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>1.80%</t>
+          <t>0.48%</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>1.82%</t>
+          <t>0.21%</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>+0.02%</t>
+          <t>-0.27%</t>
         </is>
       </c>
       <c r="J19" t="n">
-        <v>3230000</v>
+        <v>310000</v>
       </c>
       <c r="K19" t="n">
-        <v>3216000</v>
+        <v>140000</v>
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>-14,000</t>
+          <t>-170,000</t>
         </is>
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>2026-09-27_00982A_full_holdings.xlsx</t>
+          <t>2026-09-27_00403A_full_holdings.xlsx</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>00982A</t>
+          <t>00403A</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1635,55 +1635,55 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>2303</t>
+          <t>3017</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>聯電</t>
+          <t>奇鋐</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>聯電</t>
+          <t>奇鋐</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>1.62%</t>
+          <t>6.81%</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>1.56%</t>
+          <t>5.84%</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>-0.06%</t>
+          <t>-0.97%</t>
         </is>
       </c>
       <c r="J20" t="n">
-        <v>5145000</v>
+        <v>2850000</v>
       </c>
       <c r="K20" t="n">
-        <v>5116000</v>
+        <v>2500000</v>
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>-29,000</t>
+          <t>-350,000</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>2026-09-27_00982A_full_holdings.xlsx</t>
+          <t>2026-09-27_00403A_full_holdings.xlsx</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>00982A</t>
+          <t>00403A</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -1698,55 +1698,55 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>2345</t>
+          <t>3443</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>智邦</t>
+          <t>創意</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>智邦</t>
+          <t>創意</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>2.31%</t>
+          <t>3.70%</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>2.02%</t>
+          <t>3.32%</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>-0.29%</t>
+          <t>-0.38%</t>
         </is>
       </c>
       <c r="J21" t="n">
-        <v>621000</v>
+        <v>646000</v>
       </c>
       <c r="K21" t="n">
-        <v>541000</v>
+        <v>610000</v>
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>-80,000</t>
+          <t>-36,000</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>2026-09-27_00982A_full_holdings.xlsx</t>
+          <t>2026-09-27_00403A_full_holdings.xlsx</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>00982A</t>
+          <t>00403A</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -1756,438 +1756,330 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>減碼</t>
+          <t>加碼</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>2360</t>
+          <t>8996</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>致茂</t>
+          <t>高力</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>致茂</t>
+          <t>高力</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>3.75%</t>
+          <t>1.67%</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>3.69%</t>
+          <t>1.85%</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>-0.06%</t>
+          <t>+0.18%</t>
         </is>
       </c>
       <c r="J22" t="n">
-        <v>820000</v>
+        <v>1625000</v>
       </c>
       <c r="K22" t="n">
-        <v>815000</v>
+        <v>1700000</v>
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>-5,000</t>
+          <t>75,000</t>
         </is>
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>2026-09-27_00982A_full_holdings.xlsx</t>
+          <t>2026-09-27_00403A_full_holdings.xlsx</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>00982A</t>
+          <t>00985A</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>持續持有</t>
+          <t>新增</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>減碼</t>
+          <t>新納入</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>2376</t>
-        </is>
-      </c>
-      <c r="E23" t="inlineStr">
-        <is>
-          <t>技嘉</t>
-        </is>
-      </c>
+          <t>3324</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr"/>
       <c r="F23" t="inlineStr">
         <is>
-          <t>技嘉</t>
-        </is>
-      </c>
-      <c r="G23" t="inlineStr">
-        <is>
-          <t>1.26%</t>
-        </is>
-      </c>
+          <t>雙鴻</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr"/>
       <c r="H23" t="inlineStr">
         <is>
-          <t>1.24%</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr">
-        <is>
-          <t>-0.02%</t>
-        </is>
-      </c>
-      <c r="J23" t="n">
-        <v>1749000</v>
-      </c>
+          <t>0.29%</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr"/>
+      <c r="J23" t="inlineStr"/>
       <c r="K23" t="n">
-        <v>1737000</v>
-      </c>
-      <c r="L23" t="inlineStr">
-        <is>
-          <t>-12,000</t>
-        </is>
-      </c>
+        <v>18000</v>
+      </c>
+      <c r="L23" t="inlineStr"/>
       <c r="M23" t="inlineStr">
         <is>
-          <t>2026-09-27_00982A_full_holdings.xlsx</t>
+          <t>2026-09-27_00985A_full_holdings.xlsx</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>00982A</t>
+          <t>00985A</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>持續持有</t>
+          <t>新增</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>減碼</t>
+          <t>新納入</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>2377</t>
-        </is>
-      </c>
-      <c r="E24" t="inlineStr">
-        <is>
-          <t>微星</t>
-        </is>
-      </c>
+          <t>6526</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr"/>
       <c r="F24" t="inlineStr">
         <is>
-          <t>微星</t>
-        </is>
-      </c>
-      <c r="G24" t="inlineStr">
-        <is>
-          <t>1.00%</t>
-        </is>
-      </c>
+          <t>達發</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr"/>
       <c r="H24" t="inlineStr">
         <is>
-          <t>1.00%</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr">
-        <is>
-          <t>0.00%</t>
-        </is>
-      </c>
-      <c r="J24" t="n">
-        <v>3372000</v>
-      </c>
+          <t>0.80%</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr"/>
+      <c r="J24" t="inlineStr"/>
       <c r="K24" t="n">
-        <v>3344000</v>
-      </c>
-      <c r="L24" t="inlineStr">
-        <is>
-          <t>-28,000</t>
-        </is>
-      </c>
+        <v>102000</v>
+      </c>
+      <c r="L24" t="inlineStr"/>
       <c r="M24" t="inlineStr">
         <is>
-          <t>2026-09-27_00982A_full_holdings.xlsx</t>
+          <t>2026-09-27_00985A_full_holdings.xlsx</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>00982A</t>
+          <t>00985A</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>持續持有</t>
+          <t>新增</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>減碼</t>
+          <t>新納入</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>2383</t>
-        </is>
-      </c>
-      <c r="E25" t="inlineStr">
-        <is>
-          <t>台光電</t>
-        </is>
-      </c>
+          <t>6531</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr"/>
       <c r="F25" t="inlineStr">
         <is>
-          <t>台光電</t>
-        </is>
-      </c>
-      <c r="G25" t="inlineStr">
-        <is>
-          <t>3.07%</t>
-        </is>
-      </c>
+          <t>愛普*</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr"/>
       <c r="H25" t="inlineStr">
         <is>
-          <t>3.08%</t>
-        </is>
-      </c>
-      <c r="I25" t="inlineStr">
-        <is>
-          <t>+0.01%</t>
-        </is>
-      </c>
-      <c r="J25" t="n">
-        <v>311000</v>
-      </c>
+          <t>0.71%</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr"/>
+      <c r="J25" t="inlineStr"/>
       <c r="K25" t="n">
-        <v>309000</v>
-      </c>
-      <c r="L25" t="inlineStr">
-        <is>
-          <t>-2,000</t>
-        </is>
-      </c>
+        <v>76000</v>
+      </c>
+      <c r="L25" t="inlineStr"/>
       <c r="M25" t="inlineStr">
         <is>
-          <t>2026-09-27_00982A_full_holdings.xlsx</t>
+          <t>2026-09-27_00985A_full_holdings.xlsx</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>00982A</t>
+          <t>00985A</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>持續持有</t>
+          <t>刪除</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>減碼</t>
+          <t>全數賣出</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>2395</t>
+          <t>2891</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>研華</t>
-        </is>
-      </c>
-      <c r="F26" t="inlineStr">
-        <is>
-          <t>研華</t>
-        </is>
-      </c>
+          <t>中國信託金融控股</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr"/>
       <c r="G26" t="inlineStr">
         <is>
-          <t>1.56%</t>
-        </is>
-      </c>
-      <c r="H26" t="inlineStr">
-        <is>
-          <t>1.37%</t>
-        </is>
-      </c>
-      <c r="I26" t="inlineStr">
-        <is>
-          <t>-0.19%</t>
-        </is>
-      </c>
+          <t>0.19%</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr"/>
+      <c r="I26" t="inlineStr"/>
       <c r="J26" t="n">
-        <v>1128000</v>
-      </c>
-      <c r="K26" t="n">
-        <v>964000</v>
-      </c>
-      <c r="L26" t="inlineStr">
-        <is>
-          <t>-164,000</t>
-        </is>
-      </c>
+        <v>297000</v>
+      </c>
+      <c r="K26" t="inlineStr"/>
+      <c r="L26" t="inlineStr"/>
       <c r="M26" t="inlineStr">
         <is>
-          <t>2026-09-27_00982A_full_holdings.xlsx</t>
+          <t>2026-09-27_00985A_full_holdings.xlsx</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>00982A</t>
+          <t>00985A</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>持續持有</t>
+          <t>刪除</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>減碼</t>
+          <t>全數賣出</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>2428</t>
+          <t>3036</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>興勤</t>
-        </is>
-      </c>
-      <c r="F27" t="inlineStr">
-        <is>
-          <t>興勤</t>
-        </is>
-      </c>
+          <t>文曄科技</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr"/>
       <c r="G27" t="inlineStr">
         <is>
-          <t>1.14%</t>
-        </is>
-      </c>
-      <c r="H27" t="inlineStr">
-        <is>
-          <t>1.14%</t>
-        </is>
-      </c>
-      <c r="I27" t="inlineStr">
-        <is>
-          <t>0.00%</t>
-        </is>
-      </c>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr"/>
+      <c r="I27" t="inlineStr"/>
       <c r="J27" t="n">
-        <v>2285000</v>
-      </c>
-      <c r="K27" t="n">
-        <v>2268000</v>
-      </c>
-      <c r="L27" t="inlineStr">
-        <is>
-          <t>-17,000</t>
-        </is>
-      </c>
+        <v>1000</v>
+      </c>
+      <c r="K27" t="inlineStr"/>
+      <c r="L27" t="inlineStr"/>
       <c r="M27" t="inlineStr">
         <is>
-          <t>2026-09-27_00982A_full_holdings.xlsx</t>
+          <t>2026-09-27_00985A_full_holdings.xlsx</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>00982A</t>
+          <t>00985A</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>持續持有</t>
+          <t>刪除</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>減碼</t>
+          <t>全數賣出</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>2455</t>
+          <t>8299</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>全新</t>
-        </is>
-      </c>
-      <c r="F28" t="inlineStr">
-        <is>
-          <t>全新</t>
-        </is>
-      </c>
+          <t>群聯電子</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr"/>
       <c r="G28" t="inlineStr">
         <is>
-          <t>1.67%</t>
-        </is>
-      </c>
-      <c r="H28" t="inlineStr">
-        <is>
-          <t>1.67%</t>
-        </is>
-      </c>
-      <c r="I28" t="inlineStr">
-        <is>
-          <t>0.00%</t>
-        </is>
-      </c>
+          <t>0.02%</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr"/>
+      <c r="I28" t="inlineStr"/>
       <c r="J28" t="n">
-        <v>1537000</v>
-      </c>
-      <c r="K28" t="n">
-        <v>1529000</v>
-      </c>
-      <c r="L28" t="inlineStr">
-        <is>
-          <t>-8,000</t>
-        </is>
-      </c>
+        <v>1000</v>
+      </c>
+      <c r="K28" t="inlineStr"/>
+      <c r="L28" t="inlineStr"/>
       <c r="M28" t="inlineStr">
         <is>
-          <t>2026-09-27_00982A_full_holdings.xlsx</t>
+          <t>2026-09-27_00985A_full_holdings.xlsx</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>00982A</t>
+          <t>00985A</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -2202,55 +2094,55 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>2478</t>
+          <t>1504</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>大毅</t>
+          <t>東元電機</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>大毅</t>
+          <t>東元</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>1.03%</t>
+          <t>1.86%</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>1.03%</t>
+          <t>1.40%</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>0.00%</t>
+          <t>-0.46%</t>
         </is>
       </c>
       <c r="J29" t="n">
-        <v>4360000</v>
+        <v>2904000</v>
       </c>
       <c r="K29" t="n">
-        <v>4331000</v>
+        <v>2177000</v>
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>-29,000</t>
+          <t>-727,000</t>
         </is>
       </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t>2026-09-27_00982A_full_holdings.xlsx</t>
+          <t>2026-09-27_00985A_full_holdings.xlsx</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>00982A</t>
+          <t>00985A</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -2265,55 +2157,55 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>3008</t>
+          <t>2317</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>大立光</t>
+          <t>鴻海精密工業</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>大立光</t>
+          <t>鴻海</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>3.07%</t>
+          <t>2.45%</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>3.10%</t>
+          <t>2.00%</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>+0.03%</t>
+          <t>-0.45%</t>
         </is>
       </c>
       <c r="J30" t="n">
-        <v>252000</v>
+        <v>1021000</v>
       </c>
       <c r="K30" t="n">
-        <v>251000</v>
+        <v>853000</v>
       </c>
       <c r="L30" t="inlineStr">
         <is>
-          <t>-1,000</t>
+          <t>-168,000</t>
         </is>
       </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t>2026-09-27_00982A_full_holdings.xlsx</t>
+          <t>2026-09-27_00985A_full_holdings.xlsx</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>00982A</t>
+          <t>00985A</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -2328,55 +2220,55 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>3090</t>
+          <t>2376</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>日電貿</t>
+          <t>技嘉科技</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>日電貿</t>
+          <t>技嘉</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>1.07%</t>
+          <t>4.17%</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>1.07%</t>
+          <t>3.49%</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>0.00%</t>
+          <t>-0.68%</t>
         </is>
       </c>
       <c r="J31" t="n">
-        <v>3302000</v>
+        <v>1222000</v>
       </c>
       <c r="K31" t="n">
-        <v>3280000</v>
+        <v>1030000</v>
       </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t>-22,000</t>
+          <t>-192,000</t>
         </is>
       </c>
       <c r="M31" t="inlineStr">
         <is>
-          <t>2026-09-27_00982A_full_holdings.xlsx</t>
+          <t>2026-09-27_00985A_full_holdings.xlsx</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>00982A</t>
+          <t>00985A</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -2391,55 +2283,55 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>3231</t>
+          <t>3189</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>緯創</t>
+          <t>景碩科技</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>緯創</t>
+          <t>景碩</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>1.30%</t>
+          <t>1.66%</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>1.33%</t>
+          <t>1.06%</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>+0.03%</t>
+          <t>-0.60%</t>
         </is>
       </c>
       <c r="J32" t="n">
-        <v>3660000</v>
+        <v>196000</v>
       </c>
       <c r="K32" t="n">
-        <v>3638000</v>
+        <v>118000</v>
       </c>
       <c r="L32" t="inlineStr">
         <is>
-          <t>-22,000</t>
+          <t>-78,000</t>
         </is>
       </c>
       <c r="M32" t="inlineStr">
         <is>
-          <t>2026-09-27_00982A_full_holdings.xlsx</t>
+          <t>2026-09-27_00985A_full_holdings.xlsx</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>00982A</t>
+          <t>00985A</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -2454,55 +2346,55 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>3265</t>
+          <t>8046</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>台星科</t>
+          <t>南亞電路板</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>台星科</t>
+          <t>南電</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>1.19%</t>
+          <t>2.17%</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>1.21%</t>
+          <t>1.49%</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>+0.02%</t>
+          <t>-0.68%</t>
         </is>
       </c>
       <c r="J33" t="n">
-        <v>3369000</v>
+        <v>192000</v>
       </c>
       <c r="K33" t="n">
-        <v>3345000</v>
+        <v>128000</v>
       </c>
       <c r="L33" t="inlineStr">
         <is>
-          <t>-24,000</t>
+          <t>-64,000</t>
         </is>
       </c>
       <c r="M33" t="inlineStr">
         <is>
-          <t>2026-09-27_00982A_full_holdings.xlsx</t>
+          <t>2026-09-27_00985A_full_holdings.xlsx</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>00982A</t>
+          <t>00985A</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -2517,55 +2409,55 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>3711</t>
+          <t>8996</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>日月光投控</t>
+          <t>高力熱處理工業</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>日月光投控</t>
+          <t>高力</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>1.24%</t>
+          <t>1.10%</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>1.21%</t>
+          <t>0.79%</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>-0.03%</t>
+          <t>-0.31%</t>
         </is>
       </c>
       <c r="J34" t="n">
-        <v>906000</v>
+        <v>76000</v>
       </c>
       <c r="K34" t="n">
-        <v>876000</v>
+        <v>55000</v>
       </c>
       <c r="L34" t="inlineStr">
         <is>
-          <t>-30,000</t>
+          <t>-21,000</t>
         </is>
       </c>
       <c r="M34" t="inlineStr">
         <is>
-          <t>2026-09-27_00982A_full_holdings.xlsx</t>
+          <t>2026-09-27_00985A_full_holdings.xlsx</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>00982A</t>
+          <t>00992A</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -2580,55 +2472,55 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>5425</t>
+          <t>1303</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>台半</t>
+          <t>南亞</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>台半</t>
+          <t>南亞</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>1.21%</t>
+          <t>2.94%</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>1.19%</t>
+          <t>2.06%</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>-0.02%</t>
+          <t>-0.88%</t>
         </is>
       </c>
       <c r="J35" t="n">
-        <v>6403000</v>
+        <v>5445000</v>
       </c>
       <c r="K35" t="n">
-        <v>6382000</v>
+        <v>3645000</v>
       </c>
       <c r="L35" t="inlineStr">
         <is>
-          <t>-21,000</t>
+          <t>-1,800,000</t>
         </is>
       </c>
       <c r="M35" t="inlineStr">
         <is>
-          <t>2026-09-27_00982A_full_holdings.xlsx</t>
+          <t>2026-09-27_00992A_full_holdings.xlsx</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>00982A</t>
+          <t>00993A</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -2638,60 +2530,60 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>減碼</t>
+          <t>加碼</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>5483</t>
+          <t>1560</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>中美晶</t>
+          <t>中砂</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>中美晶</t>
+          <t>中砂</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>1.25%</t>
+          <t>0.86%</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>1.27%</t>
+          <t>1.00%</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>+0.02%</t>
+          <t>+0.14%</t>
         </is>
       </c>
       <c r="J36" t="n">
-        <v>3437000</v>
+        <v>93000</v>
       </c>
       <c r="K36" t="n">
-        <v>3415000</v>
+        <v>106000</v>
       </c>
       <c r="L36" t="inlineStr">
         <is>
-          <t>-22,000</t>
+          <t>13,000</t>
         </is>
       </c>
       <c r="M36" t="inlineStr">
         <is>
-          <t>2026-09-27_00982A_full_holdings.xlsx</t>
+          <t>2026-09-27_00993A_full_holdings.xlsx</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>00982A</t>
+          <t>00993A</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -2701,60 +2593,60 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>減碼</t>
+          <t>加碼</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>6139</t>
+          <t>2006</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>亞翔</t>
+          <t>東和鋼鐵</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>亞翔</t>
+          <t>東和鋼鐵</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>5.39%</t>
+          <t>0.52%</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>5.50%</t>
+          <t>0.59%</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>+0.11%</t>
+          <t>+0.07%</t>
         </is>
       </c>
       <c r="J37" t="n">
-        <v>3721000</v>
+        <v>628000</v>
       </c>
       <c r="K37" t="n">
-        <v>3697000</v>
+        <v>699000</v>
       </c>
       <c r="L37" t="inlineStr">
         <is>
-          <t>-24,000</t>
+          <t>71,000</t>
         </is>
       </c>
       <c r="M37" t="inlineStr">
         <is>
-          <t>2026-09-27_00982A_full_holdings.xlsx</t>
+          <t>2026-09-27_00993A_full_holdings.xlsx</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>00982A</t>
+          <t>00993A</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -2764,60 +2656,60 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>減碼</t>
+          <t>加碼</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>6214</t>
+          <t>2027</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>精誠</t>
+          <t>大成鋼</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>精誠</t>
+          <t>大成鋼</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>1.29%</t>
+          <t>0.19%</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>1.29%</t>
+          <t>0.21%</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>0.00%</t>
+          <t>+0.02%</t>
         </is>
       </c>
       <c r="J38" t="n">
-        <v>3460000</v>
+        <v>416000</v>
       </c>
       <c r="K38" t="n">
-        <v>3438000</v>
+        <v>459000</v>
       </c>
       <c r="L38" t="inlineStr">
         <is>
-          <t>-22,000</t>
+          <t>43,000</t>
         </is>
       </c>
       <c r="M38" t="inlineStr">
         <is>
-          <t>2026-09-27_00982A_full_holdings.xlsx</t>
+          <t>2026-09-27_00993A_full_holdings.xlsx</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>00982A</t>
+          <t>00993A</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -2827,60 +2719,60 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>減碼</t>
+          <t>加碼</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>6274</t>
+          <t>2301</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>台燿</t>
+          <t>光寶科技</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>台燿</t>
+          <t>光寶科</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>1.21%</t>
+          <t>0.22%</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>1.23%</t>
+          <t>0.25%</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>+0.02%</t>
+          <t>+0.03%</t>
         </is>
       </c>
       <c r="J39" t="n">
-        <v>421000</v>
+        <v>80000</v>
       </c>
       <c r="K39" t="n">
-        <v>418000</v>
+        <v>89000</v>
       </c>
       <c r="L39" t="inlineStr">
         <is>
-          <t>-3,000</t>
+          <t>9,000</t>
         </is>
       </c>
       <c r="M39" t="inlineStr">
         <is>
-          <t>2026-09-27_00982A_full_holdings.xlsx</t>
+          <t>2026-09-27_00993A_full_holdings.xlsx</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>00982A</t>
+          <t>00993A</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -2890,60 +2782,60 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>減碼</t>
+          <t>加碼</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>6488</t>
+          <t>2303</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>環球晶</t>
+          <t>聯電</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>環球晶</t>
+          <t>聯電</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>2.04%</t>
+          <t>2.85%</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>2.03%</t>
+          <t>2.89%</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>-0.01%</t>
+          <t>+0.04%</t>
         </is>
       </c>
       <c r="J40" t="n">
-        <v>1089000</v>
+        <v>1835000</v>
       </c>
       <c r="K40" t="n">
-        <v>1082000</v>
+        <v>1938000</v>
       </c>
       <c r="L40" t="inlineStr">
         <is>
-          <t>-7,000</t>
+          <t>103,000</t>
         </is>
       </c>
       <c r="M40" t="inlineStr">
         <is>
-          <t>2026-09-27_00982A_full_holdings.xlsx</t>
+          <t>2026-09-27_00993A_full_holdings.xlsx</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>00982A</t>
+          <t>00993A</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -2953,60 +2845,60 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>減碼</t>
+          <t>加碼</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>6672</t>
+          <t>2327</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>騰輝電子-KY</t>
+          <t>國巨*</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>騰輝電子-KY</t>
+          <t>國巨*</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>0.32%</t>
+          <t>2.03%</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>0.35%</t>
+          <t>2.18%</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>+0.03%</t>
+          <t>+0.15%</t>
         </is>
       </c>
       <c r="J41" t="n">
-        <v>530000</v>
+        <v>365000</v>
       </c>
       <c r="K41" t="n">
-        <v>527000</v>
+        <v>388000</v>
       </c>
       <c r="L41" t="inlineStr">
         <is>
-          <t>-3,000</t>
+          <t>23,000</t>
         </is>
       </c>
       <c r="M41" t="inlineStr">
         <is>
-          <t>2026-09-27_00982A_full_holdings.xlsx</t>
+          <t>2026-09-27_00993A_full_holdings.xlsx</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>00403A</t>
+          <t>00993A</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -3016,60 +2908,60 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>減碼</t>
+          <t>加碼</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>2345</t>
+          <t>2330</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>智邦</t>
+          <t>台積電</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>智邦</t>
+          <t>台積電</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>2.42%</t>
+          <t>8.42%</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>2.24%</t>
+          <t>8.32%</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>-0.18%</t>
+          <t>-0.10%</t>
         </is>
       </c>
       <c r="J42" t="n">
-        <v>1900000</v>
+        <v>347000</v>
       </c>
       <c r="K42" t="n">
-        <v>1800000</v>
+        <v>349000</v>
       </c>
       <c r="L42" t="inlineStr">
         <is>
-          <t>-100,000</t>
+          <t>2,000</t>
         </is>
       </c>
       <c r="M42" t="inlineStr">
         <is>
-          <t>2026-09-27_00403A_full_holdings.xlsx</t>
+          <t>2026-09-27_00993A_full_holdings.xlsx</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>00403A</t>
+          <t>00993A</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -3079,60 +2971,60 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>減碼</t>
+          <t>加碼</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>2360</t>
+          <t>2344</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>致茂</t>
+          <t>華邦電子</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>致茂</t>
+          <t>華邦電</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>0.48%</t>
+          <t>2.06%</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>0.21%</t>
+          <t>2.06%</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>-0.27%</t>
+          <t>0.00%</t>
         </is>
       </c>
       <c r="J43" t="n">
-        <v>310000</v>
+        <v>1228000</v>
       </c>
       <c r="K43" t="n">
-        <v>140000</v>
+        <v>1238000</v>
       </c>
       <c r="L43" t="inlineStr">
         <is>
-          <t>-170,000</t>
+          <t>10,000</t>
         </is>
       </c>
       <c r="M43" t="inlineStr">
         <is>
-          <t>2026-09-27_00403A_full_holdings.xlsx</t>
+          <t>2026-09-27_00993A_full_holdings.xlsx</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>00403A</t>
+          <t>00993A</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -3142,60 +3034,60 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>減碼</t>
+          <t>加碼</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>3017</t>
+          <t>2347</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>奇鋐</t>
+          <t>聯強</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>奇鋐</t>
+          <t>聯強</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>6.81%</t>
+          <t>0.43%</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>5.84%</t>
+          <t>0.43%</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>-0.97%</t>
+          <t>0.00%</t>
         </is>
       </c>
       <c r="J44" t="n">
-        <v>2850000</v>
+        <v>465000</v>
       </c>
       <c r="K44" t="n">
-        <v>2500000</v>
+        <v>474000</v>
       </c>
       <c r="L44" t="inlineStr">
         <is>
-          <t>-350,000</t>
+          <t>9,000</t>
         </is>
       </c>
       <c r="M44" t="inlineStr">
         <is>
-          <t>2026-09-27_00403A_full_holdings.xlsx</t>
+          <t>2026-09-27_00993A_full_holdings.xlsx</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>00403A</t>
+          <t>00993A</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -3205,60 +3097,60 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>減碼</t>
+          <t>加碼</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>3443</t>
+          <t>2360</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>創意</t>
+          <t>致茂</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>創意</t>
+          <t>致茂</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>3.70%</t>
+          <t>0.32%</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>3.32%</t>
+          <t>0.33%</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>-0.38%</t>
+          <t>+0.01%</t>
         </is>
       </c>
       <c r="J45" t="n">
-        <v>646000</v>
+        <v>14000</v>
       </c>
       <c r="K45" t="n">
-        <v>610000</v>
+        <v>15000</v>
       </c>
       <c r="L45" t="inlineStr">
         <is>
-          <t>-36,000</t>
+          <t>1,000</t>
         </is>
       </c>
       <c r="M45" t="inlineStr">
         <is>
-          <t>2026-09-27_00403A_full_holdings.xlsx</t>
+          <t>2026-09-27_00993A_full_holdings.xlsx</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>00403A</t>
+          <t>00993A</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -3273,325 +3165,433 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>8996</t>
+          <t>2383</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>高力</t>
+          <t>台光電子</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>高力</t>
+          <t>台光電</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>1.67%</t>
+          <t>4.88%</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>1.85%</t>
+          <t>4.94%</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>+0.18%</t>
+          <t>+0.06%</t>
         </is>
       </c>
       <c r="J46" t="n">
-        <v>1625000</v>
+        <v>100000</v>
       </c>
       <c r="K46" t="n">
-        <v>1700000</v>
+        <v>101000</v>
       </c>
       <c r="L46" t="inlineStr">
         <is>
-          <t>75,000</t>
+          <t>1,000</t>
         </is>
       </c>
       <c r="M46" t="inlineStr">
         <is>
-          <t>2026-09-27_00403A_full_holdings.xlsx</t>
+          <t>2026-09-27_00993A_full_holdings.xlsx</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>00985A</t>
+          <t>00993A</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>新增</t>
+          <t>持續持有</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>新納入</t>
+          <t>加碼</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>3324</t>
-        </is>
-      </c>
-      <c r="E47" t="inlineStr"/>
+          <t>2395</t>
+        </is>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>研華</t>
+        </is>
+      </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>雙鴻</t>
-        </is>
-      </c>
-      <c r="G47" t="inlineStr"/>
+          <t>研華</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>0.52%</t>
+        </is>
+      </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>0.29%</t>
-        </is>
-      </c>
-      <c r="I47" t="inlineStr"/>
-      <c r="J47" t="inlineStr"/>
+          <t>0.59%</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr">
+        <is>
+          <t>+0.07%</t>
+        </is>
+      </c>
+      <c r="J47" t="n">
+        <v>76000</v>
+      </c>
       <c r="K47" t="n">
-        <v>18000</v>
-      </c>
-      <c r="L47" t="inlineStr"/>
+        <v>84000</v>
+      </c>
+      <c r="L47" t="inlineStr">
+        <is>
+          <t>8,000</t>
+        </is>
+      </c>
       <c r="M47" t="inlineStr">
         <is>
-          <t>2026-09-27_00985A_full_holdings.xlsx</t>
+          <t>2026-09-27_00993A_full_holdings.xlsx</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>00985A</t>
+          <t>00993A</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>新增</t>
+          <t>持續持有</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>新納入</t>
+          <t>加碼</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>6526</t>
-        </is>
-      </c>
-      <c r="E48" t="inlineStr"/>
+          <t>2408</t>
+        </is>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>南亞科</t>
+        </is>
+      </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>達發</t>
-        </is>
-      </c>
-      <c r="G48" t="inlineStr"/>
+          <t>南亞科</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>3.07%</t>
+        </is>
+      </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>0.80%</t>
-        </is>
-      </c>
-      <c r="I48" t="inlineStr"/>
-      <c r="J48" t="inlineStr"/>
+          <t>3.07%</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr">
+        <is>
+          <t>0.00%</t>
+        </is>
+      </c>
+      <c r="J48" t="n">
+        <v>613000</v>
+      </c>
       <c r="K48" t="n">
-        <v>102000</v>
-      </c>
-      <c r="L48" t="inlineStr"/>
+        <v>630000</v>
+      </c>
+      <c r="L48" t="inlineStr">
+        <is>
+          <t>17,000</t>
+        </is>
+      </c>
       <c r="M48" t="inlineStr">
         <is>
-          <t>2026-09-27_00985A_full_holdings.xlsx</t>
+          <t>2026-09-27_00993A_full_holdings.xlsx</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>00985A</t>
+          <t>00993A</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>新增</t>
+          <t>持續持有</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>新納入</t>
+          <t>加碼</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>6531</t>
-        </is>
-      </c>
-      <c r="E49" t="inlineStr"/>
+          <t>2412</t>
+        </is>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>中華電</t>
+        </is>
+      </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>愛普*</t>
-        </is>
-      </c>
-      <c r="G49" t="inlineStr"/>
+          <t>中華電</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>0.45%</t>
+        </is>
+      </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>0.71%</t>
-        </is>
-      </c>
-      <c r="I49" t="inlineStr"/>
-      <c r="J49" t="inlineStr"/>
+          <t>0.50%</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr">
+        <is>
+          <t>+0.05%</t>
+        </is>
+      </c>
+      <c r="J49" t="n">
+        <v>319000</v>
+      </c>
       <c r="K49" t="n">
-        <v>76000</v>
-      </c>
-      <c r="L49" t="inlineStr"/>
+        <v>357000</v>
+      </c>
+      <c r="L49" t="inlineStr">
+        <is>
+          <t>38,000</t>
+        </is>
+      </c>
       <c r="M49" t="inlineStr">
         <is>
-          <t>2026-09-27_00985A_full_holdings.xlsx</t>
+          <t>2026-09-27_00993A_full_holdings.xlsx</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>00985A</t>
+          <t>00993A</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>刪除</t>
+          <t>持續持有</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>全數賣出</t>
+          <t>加碼</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>2891</t>
+          <t>2603</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>中國信託金融控股</t>
-        </is>
-      </c>
-      <c r="F50" t="inlineStr"/>
+          <t>長榮海運</t>
+        </is>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>長榮</t>
+        </is>
+      </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>0.19%</t>
-        </is>
-      </c>
-      <c r="H50" t="inlineStr"/>
-      <c r="I50" t="inlineStr"/>
+          <t>0.29%</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>0.32%</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr">
+        <is>
+          <t>+0.03%</t>
+        </is>
+      </c>
       <c r="J50" t="n">
-        <v>297000</v>
-      </c>
-      <c r="K50" t="inlineStr"/>
-      <c r="L50" t="inlineStr"/>
+        <v>121000</v>
+      </c>
+      <c r="K50" t="n">
+        <v>135000</v>
+      </c>
+      <c r="L50" t="inlineStr">
+        <is>
+          <t>14,000</t>
+        </is>
+      </c>
       <c r="M50" t="inlineStr">
         <is>
-          <t>2026-09-27_00985A_full_holdings.xlsx</t>
+          <t>2026-09-27_00993A_full_holdings.xlsx</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>00985A</t>
+          <t>00993A</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>刪除</t>
+          <t>持續持有</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>全數賣出</t>
+          <t>加碼</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>3036</t>
+          <t>2606</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>文曄科技</t>
-        </is>
-      </c>
-      <c r="F51" t="inlineStr"/>
+          <t>裕民</t>
+        </is>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>裕民</t>
+        </is>
+      </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="H51" t="inlineStr"/>
-      <c r="I51" t="inlineStr"/>
+          <t>0.33%</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>0.37%</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr">
+        <is>
+          <t>+0.04%</t>
+        </is>
+      </c>
       <c r="J51" t="n">
-        <v>1000</v>
-      </c>
-      <c r="K51" t="inlineStr"/>
-      <c r="L51" t="inlineStr"/>
+        <v>446000</v>
+      </c>
+      <c r="K51" t="n">
+        <v>498000</v>
+      </c>
+      <c r="L51" t="inlineStr">
+        <is>
+          <t>52,000</t>
+        </is>
+      </c>
       <c r="M51" t="inlineStr">
         <is>
-          <t>2026-09-27_00985A_full_holdings.xlsx</t>
+          <t>2026-09-27_00993A_full_holdings.xlsx</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>00985A</t>
+          <t>00993A</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>刪除</t>
+          <t>持續持有</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>全數賣出</t>
+          <t>加碼</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>8299</t>
+          <t>2618</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>群聯電子</t>
-        </is>
-      </c>
-      <c r="F52" t="inlineStr"/>
+          <t>長榮航</t>
+        </is>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>長榮航</t>
+        </is>
+      </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>0.02%</t>
-        </is>
-      </c>
-      <c r="H52" t="inlineStr"/>
-      <c r="I52" t="inlineStr"/>
+          <t>0.18%</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>0.20%</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr">
+        <is>
+          <t>+0.02%</t>
+        </is>
+      </c>
       <c r="J52" t="n">
-        <v>1000</v>
-      </c>
-      <c r="K52" t="inlineStr"/>
-      <c r="L52" t="inlineStr"/>
+        <v>429000</v>
+      </c>
+      <c r="K52" t="n">
+        <v>487000</v>
+      </c>
+      <c r="L52" t="inlineStr">
+        <is>
+          <t>58,000</t>
+        </is>
+      </c>
       <c r="M52" t="inlineStr">
         <is>
-          <t>2026-09-27_00985A_full_holdings.xlsx</t>
+          <t>2026-09-27_00993A_full_holdings.xlsx</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>00985A</t>
+          <t>00993A</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -3601,60 +3601,60 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>減碼</t>
+          <t>加碼</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>1504</t>
+          <t>3017</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>東元電機</t>
+          <t>奇鋐</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>東元</t>
+          <t>奇鋐</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>1.86%</t>
+          <t>5.33%</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>1.40%</t>
+          <t>5.65%</t>
         </is>
       </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t>-0.46%</t>
+          <t>+0.32%</t>
         </is>
       </c>
       <c r="J53" t="n">
-        <v>2904000</v>
+        <v>158000</v>
       </c>
       <c r="K53" t="n">
-        <v>2177000</v>
+        <v>164000</v>
       </c>
       <c r="L53" t="inlineStr">
         <is>
-          <t>-727,000</t>
+          <t>6,000</t>
         </is>
       </c>
       <c r="M53" t="inlineStr">
         <is>
-          <t>2026-09-27_00985A_full_holdings.xlsx</t>
+          <t>2026-09-27_00993A_full_holdings.xlsx</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>00985A</t>
+          <t>00993A</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -3664,60 +3664,60 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>減碼</t>
+          <t>加碼</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>2317</t>
+          <t>3037</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>鴻海精密工業</t>
+          <t>欣興</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>鴻海</t>
+          <t>欣興</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>2.45%</t>
+          <t>5.54%</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>2.00%</t>
+          <t>5.96%</t>
         </is>
       </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t>-0.45%</t>
+          <t>+0.42%</t>
         </is>
       </c>
       <c r="J54" t="n">
-        <v>1021000</v>
+        <v>492000</v>
       </c>
       <c r="K54" t="n">
-        <v>853000</v>
+        <v>519000</v>
       </c>
       <c r="L54" t="inlineStr">
         <is>
-          <t>-168,000</t>
+          <t>27,000</t>
         </is>
       </c>
       <c r="M54" t="inlineStr">
         <is>
-          <t>2026-09-27_00985A_full_holdings.xlsx</t>
+          <t>2026-09-27_00993A_full_holdings.xlsx</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>00985A</t>
+          <t>00993A</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -3727,60 +3727,60 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>減碼</t>
+          <t>加碼</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>2376</t>
+          <t>3189</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>技嘉科技</t>
+          <t>景碩科技</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>技嘉</t>
+          <t>景碩</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>4.17%</t>
+          <t>3.77%</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>3.49%</t>
+          <t>4.01%</t>
         </is>
       </c>
       <c r="I55" t="inlineStr">
         <is>
-          <t>-0.68%</t>
+          <t>+0.24%</t>
         </is>
       </c>
       <c r="J55" t="n">
-        <v>1222000</v>
+        <v>428000</v>
       </c>
       <c r="K55" t="n">
-        <v>1030000</v>
+        <v>431000</v>
       </c>
       <c r="L55" t="inlineStr">
         <is>
-          <t>-192,000</t>
+          <t>3,000</t>
         </is>
       </c>
       <c r="M55" t="inlineStr">
         <is>
-          <t>2026-09-27_00985A_full_holdings.xlsx</t>
+          <t>2026-09-27_00993A_full_holdings.xlsx</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>00985A</t>
+          <t>00993A</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -3790,60 +3790,60 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>減碼</t>
+          <t>加碼</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>3189</t>
+          <t>3324</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>景碩科技</t>
+          <t>雙鴻科技</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>景碩</t>
+          <t>雙鴻</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>1.66%</t>
+          <t>0.54%</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>1.06%</t>
+          <t>0.63%</t>
         </is>
       </c>
       <c r="I56" t="inlineStr">
         <is>
-          <t>-0.60%</t>
+          <t>+0.09%</t>
         </is>
       </c>
       <c r="J56" t="n">
-        <v>196000</v>
+        <v>35000</v>
       </c>
       <c r="K56" t="n">
-        <v>118000</v>
+        <v>38000</v>
       </c>
       <c r="L56" t="inlineStr">
         <is>
-          <t>-78,000</t>
+          <t>3,000</t>
         </is>
       </c>
       <c r="M56" t="inlineStr">
         <is>
-          <t>2026-09-27_00985A_full_holdings.xlsx</t>
+          <t>2026-09-27_00993A_full_holdings.xlsx</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>00985A</t>
+          <t>00993A</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -3853,60 +3853,60 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>減碼</t>
+          <t>加碼</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>8046</t>
+          <t>3406</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>南亞電路板</t>
+          <t>玉晶光</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>南電</t>
+          <t>玉晶光</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>2.17%</t>
+          <t>0.25%</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>1.49%</t>
+          <t>0.29%</t>
         </is>
       </c>
       <c r="I57" t="inlineStr">
         <is>
-          <t>-0.68%</t>
+          <t>+0.04%</t>
         </is>
       </c>
       <c r="J57" t="n">
-        <v>192000</v>
+        <v>29000</v>
       </c>
       <c r="K57" t="n">
-        <v>128000</v>
+        <v>33000</v>
       </c>
       <c r="L57" t="inlineStr">
         <is>
-          <t>-64,000</t>
+          <t>4,000</t>
         </is>
       </c>
       <c r="M57" t="inlineStr">
         <is>
-          <t>2026-09-27_00985A_full_holdings.xlsx</t>
+          <t>2026-09-27_00993A_full_holdings.xlsx</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>00985A</t>
+          <t>00993A</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -3916,60 +3916,60 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>減碼</t>
+          <t>加碼</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>8996</t>
+          <t>3443</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>高力熱處理工業</t>
+          <t>創意電子</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>高力</t>
+          <t>創意</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>1.10%</t>
+          <t>5.29%</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>0.79%</t>
+          <t>5.45%</t>
         </is>
       </c>
       <c r="I58" t="inlineStr">
         <is>
-          <t>-0.31%</t>
+          <t>+0.16%</t>
         </is>
       </c>
       <c r="J58" t="n">
-        <v>76000</v>
+        <v>65000</v>
       </c>
       <c r="K58" t="n">
-        <v>55000</v>
+        <v>66000</v>
       </c>
       <c r="L58" t="inlineStr">
         <is>
-          <t>-21,000</t>
+          <t>1,000</t>
         </is>
       </c>
       <c r="M58" t="inlineStr">
         <is>
-          <t>2026-09-27_00985A_full_holdings.xlsx</t>
+          <t>2026-09-27_00993A_full_holdings.xlsx</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>00992A</t>
+          <t>00993A</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -3979,53 +3979,53 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>減碼</t>
+          <t>加碼</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>1303</t>
+          <t>3491</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>南亞</t>
+          <t>昇達科技</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>南亞</t>
+          <t>昇達科</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>2.94%</t>
+          <t>0.15%</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>2.06%</t>
+          <t>0.17%</t>
         </is>
       </c>
       <c r="I59" t="inlineStr">
         <is>
-          <t>-0.88%</t>
+          <t>+0.02%</t>
         </is>
       </c>
       <c r="J59" t="n">
-        <v>5445000</v>
+        <v>10000</v>
       </c>
       <c r="K59" t="n">
-        <v>3645000</v>
+        <v>11000</v>
       </c>
       <c r="L59" t="inlineStr">
         <is>
-          <t>-1,800,000</t>
+          <t>1,000</t>
         </is>
       </c>
       <c r="M59" t="inlineStr">
         <is>
-          <t>2026-09-27_00992A_full_holdings.xlsx</t>
+          <t>2026-09-27_00993A_full_holdings.xlsx</t>
         </is>
       </c>
     </row>
@@ -4047,43 +4047,43 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>1560</t>
+          <t>3532</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>中砂</t>
+          <t>台勝科</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>中砂</t>
+          <t>台勝科</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>0.86%</t>
+          <t>0.30%</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>1.00%</t>
+          <t>0.35%</t>
         </is>
       </c>
       <c r="I60" t="inlineStr">
         <is>
-          <t>+0.14%</t>
+          <t>+0.05%</t>
         </is>
       </c>
       <c r="J60" t="n">
-        <v>93000</v>
+        <v>70000</v>
       </c>
       <c r="K60" t="n">
-        <v>106000</v>
+        <v>80000</v>
       </c>
       <c r="L60" t="inlineStr">
         <is>
-          <t>13,000</t>
+          <t>10,000</t>
         </is>
       </c>
       <c r="M60" t="inlineStr">
@@ -4110,43 +4110,43 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>2006</t>
+          <t>3653</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>東和鋼鐵</t>
+          <t>健策</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>東和鋼鐵</t>
+          <t>健策</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>0.52%</t>
+          <t>1.37%</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>0.59%</t>
+          <t>2.28%</t>
         </is>
       </c>
       <c r="I61" t="inlineStr">
         <is>
-          <t>+0.07%</t>
+          <t>+0.91%</t>
         </is>
       </c>
       <c r="J61" t="n">
-        <v>628000</v>
+        <v>22000</v>
       </c>
       <c r="K61" t="n">
-        <v>699000</v>
+        <v>34000</v>
       </c>
       <c r="L61" t="inlineStr">
         <is>
-          <t>71,000</t>
+          <t>12,000</t>
         </is>
       </c>
       <c r="M61" t="inlineStr">
@@ -4173,43 +4173,43 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>2027</t>
+          <t>3711</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>大成鋼</t>
+          <t>日月光投控</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>大成鋼</t>
+          <t>日月光投控</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>0.19%</t>
+          <t>0.51%</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>0.21%</t>
+          <t>0.58%</t>
         </is>
       </c>
       <c r="I62" t="inlineStr">
         <is>
-          <t>+0.02%</t>
+          <t>+0.07%</t>
         </is>
       </c>
       <c r="J62" t="n">
-        <v>416000</v>
+        <v>76000</v>
       </c>
       <c r="K62" t="n">
-        <v>459000</v>
+        <v>85000</v>
       </c>
       <c r="L62" t="inlineStr">
         <is>
-          <t>43,000</t>
+          <t>9,000</t>
         </is>
       </c>
       <c r="M62" t="inlineStr">
@@ -4236,27 +4236,27 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>2301</t>
+          <t>4904</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>光寶科技</t>
+          <t>遠傳</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>光寶科</t>
+          <t>遠傳</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>0.22%</t>
+          <t>0.24%</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>0.25%</t>
+          <t>0.27%</t>
         </is>
       </c>
       <c r="I63" t="inlineStr">
@@ -4265,14 +4265,14 @@
         </is>
       </c>
       <c r="J63" t="n">
-        <v>80000</v>
+        <v>237000</v>
       </c>
       <c r="K63" t="n">
-        <v>89000</v>
+        <v>266000</v>
       </c>
       <c r="L63" t="inlineStr">
         <is>
-          <t>9,000</t>
+          <t>29,000</t>
         </is>
       </c>
       <c r="M63" t="inlineStr">
@@ -4299,43 +4299,43 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>2303</t>
+          <t>6223</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>聯電</t>
+          <t>旺矽</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>聯電</t>
+          <t>旺矽</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>2.85%</t>
+          <t>4.37%</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>2.89%</t>
+          <t>4.30%</t>
         </is>
       </c>
       <c r="I64" t="inlineStr">
         <is>
-          <t>+0.04%</t>
+          <t>-0.07%</t>
         </is>
       </c>
       <c r="J64" t="n">
-        <v>1835000</v>
+        <v>80000</v>
       </c>
       <c r="K64" t="n">
-        <v>1938000</v>
+        <v>82000</v>
       </c>
       <c r="L64" t="inlineStr">
         <is>
-          <t>103,000</t>
+          <t>2,000</t>
         </is>
       </c>
       <c r="M64" t="inlineStr">
@@ -4362,43 +4362,43 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>2327</t>
+          <t>6505</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>國巨*</t>
+          <t>台塑石化</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>國巨*</t>
+          <t>台塑化</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>2.03%</t>
+          <t>0.29%</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>2.18%</t>
+          <t>0.32%</t>
         </is>
       </c>
       <c r="I65" t="inlineStr">
         <is>
-          <t>+0.15%</t>
+          <t>+0.03%</t>
         </is>
       </c>
       <c r="J65" t="n">
-        <v>365000</v>
+        <v>339000</v>
       </c>
       <c r="K65" t="n">
-        <v>388000</v>
+        <v>378000</v>
       </c>
       <c r="L65" t="inlineStr">
         <is>
-          <t>23,000</t>
+          <t>39,000</t>
         </is>
       </c>
       <c r="M65" t="inlineStr">
@@ -4425,43 +4425,43 @@
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>2330</t>
+          <t>8046</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>台積電</t>
+          <t>南電</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>台積電</t>
+          <t>南電</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>8.42%</t>
+          <t>2.90%</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>8.32%</t>
+          <t>3.05%</t>
         </is>
       </c>
       <c r="I66" t="inlineStr">
         <is>
-          <t>-0.10%</t>
+          <t>+0.15%</t>
         </is>
       </c>
       <c r="J66" t="n">
-        <v>347000</v>
+        <v>247000</v>
       </c>
       <c r="K66" t="n">
-        <v>349000</v>
+        <v>254000</v>
       </c>
       <c r="L66" t="inlineStr">
         <is>
-          <t>2,000</t>
+          <t>7,000</t>
         </is>
       </c>
       <c r="M66" t="inlineStr">
@@ -4473,7 +4473,7 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>00993A</t>
+          <t>00400A</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -4483,60 +4483,60 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>加碼</t>
+          <t>減碼</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>2344</t>
+          <t>2454</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>華邦電子</t>
+          <t>聯發科</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>華邦電</t>
+          <t>聯發科</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>2.06%</t>
+          <t>7.99%</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>2.06%</t>
+          <t>7.06%</t>
         </is>
       </c>
       <c r="I67" t="inlineStr">
         <is>
-          <t>0.00%</t>
+          <t>-0.93%</t>
         </is>
       </c>
       <c r="J67" t="n">
-        <v>1228000</v>
+        <v>442000</v>
       </c>
       <c r="K67" t="n">
-        <v>1238000</v>
+        <v>413000</v>
       </c>
       <c r="L67" t="inlineStr">
         <is>
-          <t>10,000</t>
+          <t>-29,000</t>
         </is>
       </c>
       <c r="M67" t="inlineStr">
         <is>
-          <t>2026-09-27_00993A_full_holdings.xlsx</t>
+          <t>2026-09-27_00400A_full_holdings.xlsx</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>00993A</t>
+          <t>00400A</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -4546,60 +4546,60 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>加碼</t>
+          <t>減碼</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>2347</t>
+          <t>3443</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>聯強</t>
+          <t>創意</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>聯強</t>
+          <t>創意</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>0.43%</t>
+          <t>5.04%</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>0.43%</t>
+          <t>4.27%</t>
         </is>
       </c>
       <c r="I68" t="inlineStr">
         <is>
-          <t>0.00%</t>
+          <t>-0.77%</t>
         </is>
       </c>
       <c r="J68" t="n">
-        <v>465000</v>
+        <v>173000</v>
       </c>
       <c r="K68" t="n">
-        <v>474000</v>
+        <v>155000</v>
       </c>
       <c r="L68" t="inlineStr">
         <is>
-          <t>9,000</t>
+          <t>-18,000</t>
         </is>
       </c>
       <c r="M68" t="inlineStr">
         <is>
-          <t>2026-09-27_00993A_full_holdings.xlsx</t>
+          <t>2026-09-27_00400A_full_holdings.xlsx</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>00993A</t>
+          <t>00400A</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -4614,1558 +4614,46 @@
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>2360</t>
+          <t>6505</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>致茂</t>
+          <t>台塑化</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>致茂</t>
+          <t>台塑化</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>0.32%</t>
+          <t>1.46%</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>0.33%</t>
+          <t>2.02%</t>
         </is>
       </c>
       <c r="I69" t="inlineStr">
         <is>
-          <t>+0.01%</t>
+          <t>+0.56%</t>
         </is>
       </c>
       <c r="J69" t="n">
-        <v>14000</v>
+        <v>4903000</v>
       </c>
       <c r="K69" t="n">
-        <v>15000</v>
+        <v>6147000</v>
       </c>
       <c r="L69" t="inlineStr">
         <is>
-          <t>1,000</t>
+          <t>1,244,000</t>
         </is>
       </c>
       <c r="M69" t="inlineStr">
-        <is>
-          <t>2026-09-27_00993A_full_holdings.xlsx</t>
-        </is>
-      </c>
-    </row>
-    <row r="70">
-      <c r="A70" t="inlineStr">
-        <is>
-          <t>00993A</t>
-        </is>
-      </c>
-      <c r="B70" t="inlineStr">
-        <is>
-          <t>持續持有</t>
-        </is>
-      </c>
-      <c r="C70" t="inlineStr">
-        <is>
-          <t>加碼</t>
-        </is>
-      </c>
-      <c r="D70" t="inlineStr">
-        <is>
-          <t>2383</t>
-        </is>
-      </c>
-      <c r="E70" t="inlineStr">
-        <is>
-          <t>台光電子</t>
-        </is>
-      </c>
-      <c r="F70" t="inlineStr">
-        <is>
-          <t>台光電</t>
-        </is>
-      </c>
-      <c r="G70" t="inlineStr">
-        <is>
-          <t>4.88%</t>
-        </is>
-      </c>
-      <c r="H70" t="inlineStr">
-        <is>
-          <t>4.94%</t>
-        </is>
-      </c>
-      <c r="I70" t="inlineStr">
-        <is>
-          <t>+0.06%</t>
-        </is>
-      </c>
-      <c r="J70" t="n">
-        <v>100000</v>
-      </c>
-      <c r="K70" t="n">
-        <v>101000</v>
-      </c>
-      <c r="L70" t="inlineStr">
-        <is>
-          <t>1,000</t>
-        </is>
-      </c>
-      <c r="M70" t="inlineStr">
-        <is>
-          <t>2026-09-27_00993A_full_holdings.xlsx</t>
-        </is>
-      </c>
-    </row>
-    <row r="71">
-      <c r="A71" t="inlineStr">
-        <is>
-          <t>00993A</t>
-        </is>
-      </c>
-      <c r="B71" t="inlineStr">
-        <is>
-          <t>持續持有</t>
-        </is>
-      </c>
-      <c r="C71" t="inlineStr">
-        <is>
-          <t>加碼</t>
-        </is>
-      </c>
-      <c r="D71" t="inlineStr">
-        <is>
-          <t>2395</t>
-        </is>
-      </c>
-      <c r="E71" t="inlineStr">
-        <is>
-          <t>研華</t>
-        </is>
-      </c>
-      <c r="F71" t="inlineStr">
-        <is>
-          <t>研華</t>
-        </is>
-      </c>
-      <c r="G71" t="inlineStr">
-        <is>
-          <t>0.52%</t>
-        </is>
-      </c>
-      <c r="H71" t="inlineStr">
-        <is>
-          <t>0.59%</t>
-        </is>
-      </c>
-      <c r="I71" t="inlineStr">
-        <is>
-          <t>+0.07%</t>
-        </is>
-      </c>
-      <c r="J71" t="n">
-        <v>76000</v>
-      </c>
-      <c r="K71" t="n">
-        <v>84000</v>
-      </c>
-      <c r="L71" t="inlineStr">
-        <is>
-          <t>8,000</t>
-        </is>
-      </c>
-      <c r="M71" t="inlineStr">
-        <is>
-          <t>2026-09-27_00993A_full_holdings.xlsx</t>
-        </is>
-      </c>
-    </row>
-    <row r="72">
-      <c r="A72" t="inlineStr">
-        <is>
-          <t>00993A</t>
-        </is>
-      </c>
-      <c r="B72" t="inlineStr">
-        <is>
-          <t>持續持有</t>
-        </is>
-      </c>
-      <c r="C72" t="inlineStr">
-        <is>
-          <t>加碼</t>
-        </is>
-      </c>
-      <c r="D72" t="inlineStr">
-        <is>
-          <t>2408</t>
-        </is>
-      </c>
-      <c r="E72" t="inlineStr">
-        <is>
-          <t>南亞科</t>
-        </is>
-      </c>
-      <c r="F72" t="inlineStr">
-        <is>
-          <t>南亞科</t>
-        </is>
-      </c>
-      <c r="G72" t="inlineStr">
-        <is>
-          <t>3.07%</t>
-        </is>
-      </c>
-      <c r="H72" t="inlineStr">
-        <is>
-          <t>3.07%</t>
-        </is>
-      </c>
-      <c r="I72" t="inlineStr">
-        <is>
-          <t>0.00%</t>
-        </is>
-      </c>
-      <c r="J72" t="n">
-        <v>613000</v>
-      </c>
-      <c r="K72" t="n">
-        <v>630000</v>
-      </c>
-      <c r="L72" t="inlineStr">
-        <is>
-          <t>17,000</t>
-        </is>
-      </c>
-      <c r="M72" t="inlineStr">
-        <is>
-          <t>2026-09-27_00993A_full_holdings.xlsx</t>
-        </is>
-      </c>
-    </row>
-    <row r="73">
-      <c r="A73" t="inlineStr">
-        <is>
-          <t>00993A</t>
-        </is>
-      </c>
-      <c r="B73" t="inlineStr">
-        <is>
-          <t>持續持有</t>
-        </is>
-      </c>
-      <c r="C73" t="inlineStr">
-        <is>
-          <t>加碼</t>
-        </is>
-      </c>
-      <c r="D73" t="inlineStr">
-        <is>
-          <t>2412</t>
-        </is>
-      </c>
-      <c r="E73" t="inlineStr">
-        <is>
-          <t>中華電</t>
-        </is>
-      </c>
-      <c r="F73" t="inlineStr">
-        <is>
-          <t>中華電</t>
-        </is>
-      </c>
-      <c r="G73" t="inlineStr">
-        <is>
-          <t>0.45%</t>
-        </is>
-      </c>
-      <c r="H73" t="inlineStr">
-        <is>
-          <t>0.50%</t>
-        </is>
-      </c>
-      <c r="I73" t="inlineStr">
-        <is>
-          <t>+0.05%</t>
-        </is>
-      </c>
-      <c r="J73" t="n">
-        <v>319000</v>
-      </c>
-      <c r="K73" t="n">
-        <v>357000</v>
-      </c>
-      <c r="L73" t="inlineStr">
-        <is>
-          <t>38,000</t>
-        </is>
-      </c>
-      <c r="M73" t="inlineStr">
-        <is>
-          <t>2026-09-27_00993A_full_holdings.xlsx</t>
-        </is>
-      </c>
-    </row>
-    <row r="74">
-      <c r="A74" t="inlineStr">
-        <is>
-          <t>00993A</t>
-        </is>
-      </c>
-      <c r="B74" t="inlineStr">
-        <is>
-          <t>持續持有</t>
-        </is>
-      </c>
-      <c r="C74" t="inlineStr">
-        <is>
-          <t>加碼</t>
-        </is>
-      </c>
-      <c r="D74" t="inlineStr">
-        <is>
-          <t>2603</t>
-        </is>
-      </c>
-      <c r="E74" t="inlineStr">
-        <is>
-          <t>長榮海運</t>
-        </is>
-      </c>
-      <c r="F74" t="inlineStr">
-        <is>
-          <t>長榮</t>
-        </is>
-      </c>
-      <c r="G74" t="inlineStr">
-        <is>
-          <t>0.29%</t>
-        </is>
-      </c>
-      <c r="H74" t="inlineStr">
-        <is>
-          <t>0.32%</t>
-        </is>
-      </c>
-      <c r="I74" t="inlineStr">
-        <is>
-          <t>+0.03%</t>
-        </is>
-      </c>
-      <c r="J74" t="n">
-        <v>121000</v>
-      </c>
-      <c r="K74" t="n">
-        <v>135000</v>
-      </c>
-      <c r="L74" t="inlineStr">
-        <is>
-          <t>14,000</t>
-        </is>
-      </c>
-      <c r="M74" t="inlineStr">
-        <is>
-          <t>2026-09-27_00993A_full_holdings.xlsx</t>
-        </is>
-      </c>
-    </row>
-    <row r="75">
-      <c r="A75" t="inlineStr">
-        <is>
-          <t>00993A</t>
-        </is>
-      </c>
-      <c r="B75" t="inlineStr">
-        <is>
-          <t>持續持有</t>
-        </is>
-      </c>
-      <c r="C75" t="inlineStr">
-        <is>
-          <t>加碼</t>
-        </is>
-      </c>
-      <c r="D75" t="inlineStr">
-        <is>
-          <t>2606</t>
-        </is>
-      </c>
-      <c r="E75" t="inlineStr">
-        <is>
-          <t>裕民</t>
-        </is>
-      </c>
-      <c r="F75" t="inlineStr">
-        <is>
-          <t>裕民</t>
-        </is>
-      </c>
-      <c r="G75" t="inlineStr">
-        <is>
-          <t>0.33%</t>
-        </is>
-      </c>
-      <c r="H75" t="inlineStr">
-        <is>
-          <t>0.37%</t>
-        </is>
-      </c>
-      <c r="I75" t="inlineStr">
-        <is>
-          <t>+0.04%</t>
-        </is>
-      </c>
-      <c r="J75" t="n">
-        <v>446000</v>
-      </c>
-      <c r="K75" t="n">
-        <v>498000</v>
-      </c>
-      <c r="L75" t="inlineStr">
-        <is>
-          <t>52,000</t>
-        </is>
-      </c>
-      <c r="M75" t="inlineStr">
-        <is>
-          <t>2026-09-27_00993A_full_holdings.xlsx</t>
-        </is>
-      </c>
-    </row>
-    <row r="76">
-      <c r="A76" t="inlineStr">
-        <is>
-          <t>00993A</t>
-        </is>
-      </c>
-      <c r="B76" t="inlineStr">
-        <is>
-          <t>持續持有</t>
-        </is>
-      </c>
-      <c r="C76" t="inlineStr">
-        <is>
-          <t>加碼</t>
-        </is>
-      </c>
-      <c r="D76" t="inlineStr">
-        <is>
-          <t>2618</t>
-        </is>
-      </c>
-      <c r="E76" t="inlineStr">
-        <is>
-          <t>長榮航</t>
-        </is>
-      </c>
-      <c r="F76" t="inlineStr">
-        <is>
-          <t>長榮航</t>
-        </is>
-      </c>
-      <c r="G76" t="inlineStr">
-        <is>
-          <t>0.18%</t>
-        </is>
-      </c>
-      <c r="H76" t="inlineStr">
-        <is>
-          <t>0.20%</t>
-        </is>
-      </c>
-      <c r="I76" t="inlineStr">
-        <is>
-          <t>+0.02%</t>
-        </is>
-      </c>
-      <c r="J76" t="n">
-        <v>429000</v>
-      </c>
-      <c r="K76" t="n">
-        <v>487000</v>
-      </c>
-      <c r="L76" t="inlineStr">
-        <is>
-          <t>58,000</t>
-        </is>
-      </c>
-      <c r="M76" t="inlineStr">
-        <is>
-          <t>2026-09-27_00993A_full_holdings.xlsx</t>
-        </is>
-      </c>
-    </row>
-    <row r="77">
-      <c r="A77" t="inlineStr">
-        <is>
-          <t>00993A</t>
-        </is>
-      </c>
-      <c r="B77" t="inlineStr">
-        <is>
-          <t>持續持有</t>
-        </is>
-      </c>
-      <c r="C77" t="inlineStr">
-        <is>
-          <t>加碼</t>
-        </is>
-      </c>
-      <c r="D77" t="inlineStr">
-        <is>
-          <t>3017</t>
-        </is>
-      </c>
-      <c r="E77" t="inlineStr">
-        <is>
-          <t>奇鋐</t>
-        </is>
-      </c>
-      <c r="F77" t="inlineStr">
-        <is>
-          <t>奇鋐</t>
-        </is>
-      </c>
-      <c r="G77" t="inlineStr">
-        <is>
-          <t>5.33%</t>
-        </is>
-      </c>
-      <c r="H77" t="inlineStr">
-        <is>
-          <t>5.65%</t>
-        </is>
-      </c>
-      <c r="I77" t="inlineStr">
-        <is>
-          <t>+0.32%</t>
-        </is>
-      </c>
-      <c r="J77" t="n">
-        <v>158000</v>
-      </c>
-      <c r="K77" t="n">
-        <v>164000</v>
-      </c>
-      <c r="L77" t="inlineStr">
-        <is>
-          <t>6,000</t>
-        </is>
-      </c>
-      <c r="M77" t="inlineStr">
-        <is>
-          <t>2026-09-27_00993A_full_holdings.xlsx</t>
-        </is>
-      </c>
-    </row>
-    <row r="78">
-      <c r="A78" t="inlineStr">
-        <is>
-          <t>00993A</t>
-        </is>
-      </c>
-      <c r="B78" t="inlineStr">
-        <is>
-          <t>持續持有</t>
-        </is>
-      </c>
-      <c r="C78" t="inlineStr">
-        <is>
-          <t>加碼</t>
-        </is>
-      </c>
-      <c r="D78" t="inlineStr">
-        <is>
-          <t>3037</t>
-        </is>
-      </c>
-      <c r="E78" t="inlineStr">
-        <is>
-          <t>欣興</t>
-        </is>
-      </c>
-      <c r="F78" t="inlineStr">
-        <is>
-          <t>欣興</t>
-        </is>
-      </c>
-      <c r="G78" t="inlineStr">
-        <is>
-          <t>5.54%</t>
-        </is>
-      </c>
-      <c r="H78" t="inlineStr">
-        <is>
-          <t>5.96%</t>
-        </is>
-      </c>
-      <c r="I78" t="inlineStr">
-        <is>
-          <t>+0.42%</t>
-        </is>
-      </c>
-      <c r="J78" t="n">
-        <v>492000</v>
-      </c>
-      <c r="K78" t="n">
-        <v>519000</v>
-      </c>
-      <c r="L78" t="inlineStr">
-        <is>
-          <t>27,000</t>
-        </is>
-      </c>
-      <c r="M78" t="inlineStr">
-        <is>
-          <t>2026-09-27_00993A_full_holdings.xlsx</t>
-        </is>
-      </c>
-    </row>
-    <row r="79">
-      <c r="A79" t="inlineStr">
-        <is>
-          <t>00993A</t>
-        </is>
-      </c>
-      <c r="B79" t="inlineStr">
-        <is>
-          <t>持續持有</t>
-        </is>
-      </c>
-      <c r="C79" t="inlineStr">
-        <is>
-          <t>加碼</t>
-        </is>
-      </c>
-      <c r="D79" t="inlineStr">
-        <is>
-          <t>3189</t>
-        </is>
-      </c>
-      <c r="E79" t="inlineStr">
-        <is>
-          <t>景碩科技</t>
-        </is>
-      </c>
-      <c r="F79" t="inlineStr">
-        <is>
-          <t>景碩</t>
-        </is>
-      </c>
-      <c r="G79" t="inlineStr">
-        <is>
-          <t>3.77%</t>
-        </is>
-      </c>
-      <c r="H79" t="inlineStr">
-        <is>
-          <t>4.01%</t>
-        </is>
-      </c>
-      <c r="I79" t="inlineStr">
-        <is>
-          <t>+0.24%</t>
-        </is>
-      </c>
-      <c r="J79" t="n">
-        <v>428000</v>
-      </c>
-      <c r="K79" t="n">
-        <v>431000</v>
-      </c>
-      <c r="L79" t="inlineStr">
-        <is>
-          <t>3,000</t>
-        </is>
-      </c>
-      <c r="M79" t="inlineStr">
-        <is>
-          <t>2026-09-27_00993A_full_holdings.xlsx</t>
-        </is>
-      </c>
-    </row>
-    <row r="80">
-      <c r="A80" t="inlineStr">
-        <is>
-          <t>00993A</t>
-        </is>
-      </c>
-      <c r="B80" t="inlineStr">
-        <is>
-          <t>持續持有</t>
-        </is>
-      </c>
-      <c r="C80" t="inlineStr">
-        <is>
-          <t>加碼</t>
-        </is>
-      </c>
-      <c r="D80" t="inlineStr">
-        <is>
-          <t>3324</t>
-        </is>
-      </c>
-      <c r="E80" t="inlineStr">
-        <is>
-          <t>雙鴻科技</t>
-        </is>
-      </c>
-      <c r="F80" t="inlineStr">
-        <is>
-          <t>雙鴻</t>
-        </is>
-      </c>
-      <c r="G80" t="inlineStr">
-        <is>
-          <t>0.54%</t>
-        </is>
-      </c>
-      <c r="H80" t="inlineStr">
-        <is>
-          <t>0.63%</t>
-        </is>
-      </c>
-      <c r="I80" t="inlineStr">
-        <is>
-          <t>+0.09%</t>
-        </is>
-      </c>
-      <c r="J80" t="n">
-        <v>35000</v>
-      </c>
-      <c r="K80" t="n">
-        <v>38000</v>
-      </c>
-      <c r="L80" t="inlineStr">
-        <is>
-          <t>3,000</t>
-        </is>
-      </c>
-      <c r="M80" t="inlineStr">
-        <is>
-          <t>2026-09-27_00993A_full_holdings.xlsx</t>
-        </is>
-      </c>
-    </row>
-    <row r="81">
-      <c r="A81" t="inlineStr">
-        <is>
-          <t>00993A</t>
-        </is>
-      </c>
-      <c r="B81" t="inlineStr">
-        <is>
-          <t>持續持有</t>
-        </is>
-      </c>
-      <c r="C81" t="inlineStr">
-        <is>
-          <t>加碼</t>
-        </is>
-      </c>
-      <c r="D81" t="inlineStr">
-        <is>
-          <t>3406</t>
-        </is>
-      </c>
-      <c r="E81" t="inlineStr">
-        <is>
-          <t>玉晶光</t>
-        </is>
-      </c>
-      <c r="F81" t="inlineStr">
-        <is>
-          <t>玉晶光</t>
-        </is>
-      </c>
-      <c r="G81" t="inlineStr">
-        <is>
-          <t>0.25%</t>
-        </is>
-      </c>
-      <c r="H81" t="inlineStr">
-        <is>
-          <t>0.29%</t>
-        </is>
-      </c>
-      <c r="I81" t="inlineStr">
-        <is>
-          <t>+0.04%</t>
-        </is>
-      </c>
-      <c r="J81" t="n">
-        <v>29000</v>
-      </c>
-      <c r="K81" t="n">
-        <v>33000</v>
-      </c>
-      <c r="L81" t="inlineStr">
-        <is>
-          <t>4,000</t>
-        </is>
-      </c>
-      <c r="M81" t="inlineStr">
-        <is>
-          <t>2026-09-27_00993A_full_holdings.xlsx</t>
-        </is>
-      </c>
-    </row>
-    <row r="82">
-      <c r="A82" t="inlineStr">
-        <is>
-          <t>00993A</t>
-        </is>
-      </c>
-      <c r="B82" t="inlineStr">
-        <is>
-          <t>持續持有</t>
-        </is>
-      </c>
-      <c r="C82" t="inlineStr">
-        <is>
-          <t>加碼</t>
-        </is>
-      </c>
-      <c r="D82" t="inlineStr">
-        <is>
-          <t>3443</t>
-        </is>
-      </c>
-      <c r="E82" t="inlineStr">
-        <is>
-          <t>創意電子</t>
-        </is>
-      </c>
-      <c r="F82" t="inlineStr">
-        <is>
-          <t>創意</t>
-        </is>
-      </c>
-      <c r="G82" t="inlineStr">
-        <is>
-          <t>5.29%</t>
-        </is>
-      </c>
-      <c r="H82" t="inlineStr">
-        <is>
-          <t>5.45%</t>
-        </is>
-      </c>
-      <c r="I82" t="inlineStr">
-        <is>
-          <t>+0.16%</t>
-        </is>
-      </c>
-      <c r="J82" t="n">
-        <v>65000</v>
-      </c>
-      <c r="K82" t="n">
-        <v>66000</v>
-      </c>
-      <c r="L82" t="inlineStr">
-        <is>
-          <t>1,000</t>
-        </is>
-      </c>
-      <c r="M82" t="inlineStr">
-        <is>
-          <t>2026-09-27_00993A_full_holdings.xlsx</t>
-        </is>
-      </c>
-    </row>
-    <row r="83">
-      <c r="A83" t="inlineStr">
-        <is>
-          <t>00993A</t>
-        </is>
-      </c>
-      <c r="B83" t="inlineStr">
-        <is>
-          <t>持續持有</t>
-        </is>
-      </c>
-      <c r="C83" t="inlineStr">
-        <is>
-          <t>加碼</t>
-        </is>
-      </c>
-      <c r="D83" t="inlineStr">
-        <is>
-          <t>3491</t>
-        </is>
-      </c>
-      <c r="E83" t="inlineStr">
-        <is>
-          <t>昇達科技</t>
-        </is>
-      </c>
-      <c r="F83" t="inlineStr">
-        <is>
-          <t>昇達科</t>
-        </is>
-      </c>
-      <c r="G83" t="inlineStr">
-        <is>
-          <t>0.15%</t>
-        </is>
-      </c>
-      <c r="H83" t="inlineStr">
-        <is>
-          <t>0.17%</t>
-        </is>
-      </c>
-      <c r="I83" t="inlineStr">
-        <is>
-          <t>+0.02%</t>
-        </is>
-      </c>
-      <c r="J83" t="n">
-        <v>10000</v>
-      </c>
-      <c r="K83" t="n">
-        <v>11000</v>
-      </c>
-      <c r="L83" t="inlineStr">
-        <is>
-          <t>1,000</t>
-        </is>
-      </c>
-      <c r="M83" t="inlineStr">
-        <is>
-          <t>2026-09-27_00993A_full_holdings.xlsx</t>
-        </is>
-      </c>
-    </row>
-    <row r="84">
-      <c r="A84" t="inlineStr">
-        <is>
-          <t>00993A</t>
-        </is>
-      </c>
-      <c r="B84" t="inlineStr">
-        <is>
-          <t>持續持有</t>
-        </is>
-      </c>
-      <c r="C84" t="inlineStr">
-        <is>
-          <t>加碼</t>
-        </is>
-      </c>
-      <c r="D84" t="inlineStr">
-        <is>
-          <t>3532</t>
-        </is>
-      </c>
-      <c r="E84" t="inlineStr">
-        <is>
-          <t>台勝科</t>
-        </is>
-      </c>
-      <c r="F84" t="inlineStr">
-        <is>
-          <t>台勝科</t>
-        </is>
-      </c>
-      <c r="G84" t="inlineStr">
-        <is>
-          <t>0.30%</t>
-        </is>
-      </c>
-      <c r="H84" t="inlineStr">
-        <is>
-          <t>0.35%</t>
-        </is>
-      </c>
-      <c r="I84" t="inlineStr">
-        <is>
-          <t>+0.05%</t>
-        </is>
-      </c>
-      <c r="J84" t="n">
-        <v>70000</v>
-      </c>
-      <c r="K84" t="n">
-        <v>80000</v>
-      </c>
-      <c r="L84" t="inlineStr">
-        <is>
-          <t>10,000</t>
-        </is>
-      </c>
-      <c r="M84" t="inlineStr">
-        <is>
-          <t>2026-09-27_00993A_full_holdings.xlsx</t>
-        </is>
-      </c>
-    </row>
-    <row r="85">
-      <c r="A85" t="inlineStr">
-        <is>
-          <t>00993A</t>
-        </is>
-      </c>
-      <c r="B85" t="inlineStr">
-        <is>
-          <t>持續持有</t>
-        </is>
-      </c>
-      <c r="C85" t="inlineStr">
-        <is>
-          <t>加碼</t>
-        </is>
-      </c>
-      <c r="D85" t="inlineStr">
-        <is>
-          <t>3653</t>
-        </is>
-      </c>
-      <c r="E85" t="inlineStr">
-        <is>
-          <t>健策</t>
-        </is>
-      </c>
-      <c r="F85" t="inlineStr">
-        <is>
-          <t>健策</t>
-        </is>
-      </c>
-      <c r="G85" t="inlineStr">
-        <is>
-          <t>1.37%</t>
-        </is>
-      </c>
-      <c r="H85" t="inlineStr">
-        <is>
-          <t>2.28%</t>
-        </is>
-      </c>
-      <c r="I85" t="inlineStr">
-        <is>
-          <t>+0.91%</t>
-        </is>
-      </c>
-      <c r="J85" t="n">
-        <v>22000</v>
-      </c>
-      <c r="K85" t="n">
-        <v>34000</v>
-      </c>
-      <c r="L85" t="inlineStr">
-        <is>
-          <t>12,000</t>
-        </is>
-      </c>
-      <c r="M85" t="inlineStr">
-        <is>
-          <t>2026-09-27_00993A_full_holdings.xlsx</t>
-        </is>
-      </c>
-    </row>
-    <row r="86">
-      <c r="A86" t="inlineStr">
-        <is>
-          <t>00993A</t>
-        </is>
-      </c>
-      <c r="B86" t="inlineStr">
-        <is>
-          <t>持續持有</t>
-        </is>
-      </c>
-      <c r="C86" t="inlineStr">
-        <is>
-          <t>加碼</t>
-        </is>
-      </c>
-      <c r="D86" t="inlineStr">
-        <is>
-          <t>3711</t>
-        </is>
-      </c>
-      <c r="E86" t="inlineStr">
-        <is>
-          <t>日月光投控</t>
-        </is>
-      </c>
-      <c r="F86" t="inlineStr">
-        <is>
-          <t>日月光投控</t>
-        </is>
-      </c>
-      <c r="G86" t="inlineStr">
-        <is>
-          <t>0.51%</t>
-        </is>
-      </c>
-      <c r="H86" t="inlineStr">
-        <is>
-          <t>0.58%</t>
-        </is>
-      </c>
-      <c r="I86" t="inlineStr">
-        <is>
-          <t>+0.07%</t>
-        </is>
-      </c>
-      <c r="J86" t="n">
-        <v>76000</v>
-      </c>
-      <c r="K86" t="n">
-        <v>85000</v>
-      </c>
-      <c r="L86" t="inlineStr">
-        <is>
-          <t>9,000</t>
-        </is>
-      </c>
-      <c r="M86" t="inlineStr">
-        <is>
-          <t>2026-09-27_00993A_full_holdings.xlsx</t>
-        </is>
-      </c>
-    </row>
-    <row r="87">
-      <c r="A87" t="inlineStr">
-        <is>
-          <t>00993A</t>
-        </is>
-      </c>
-      <c r="B87" t="inlineStr">
-        <is>
-          <t>持續持有</t>
-        </is>
-      </c>
-      <c r="C87" t="inlineStr">
-        <is>
-          <t>加碼</t>
-        </is>
-      </c>
-      <c r="D87" t="inlineStr">
-        <is>
-          <t>4904</t>
-        </is>
-      </c>
-      <c r="E87" t="inlineStr">
-        <is>
-          <t>遠傳</t>
-        </is>
-      </c>
-      <c r="F87" t="inlineStr">
-        <is>
-          <t>遠傳</t>
-        </is>
-      </c>
-      <c r="G87" t="inlineStr">
-        <is>
-          <t>0.24%</t>
-        </is>
-      </c>
-      <c r="H87" t="inlineStr">
-        <is>
-          <t>0.27%</t>
-        </is>
-      </c>
-      <c r="I87" t="inlineStr">
-        <is>
-          <t>+0.03%</t>
-        </is>
-      </c>
-      <c r="J87" t="n">
-        <v>237000</v>
-      </c>
-      <c r="K87" t="n">
-        <v>266000</v>
-      </c>
-      <c r="L87" t="inlineStr">
-        <is>
-          <t>29,000</t>
-        </is>
-      </c>
-      <c r="M87" t="inlineStr">
-        <is>
-          <t>2026-09-27_00993A_full_holdings.xlsx</t>
-        </is>
-      </c>
-    </row>
-    <row r="88">
-      <c r="A88" t="inlineStr">
-        <is>
-          <t>00993A</t>
-        </is>
-      </c>
-      <c r="B88" t="inlineStr">
-        <is>
-          <t>持續持有</t>
-        </is>
-      </c>
-      <c r="C88" t="inlineStr">
-        <is>
-          <t>加碼</t>
-        </is>
-      </c>
-      <c r="D88" t="inlineStr">
-        <is>
-          <t>6223</t>
-        </is>
-      </c>
-      <c r="E88" t="inlineStr">
-        <is>
-          <t>旺矽</t>
-        </is>
-      </c>
-      <c r="F88" t="inlineStr">
-        <is>
-          <t>旺矽</t>
-        </is>
-      </c>
-      <c r="G88" t="inlineStr">
-        <is>
-          <t>4.37%</t>
-        </is>
-      </c>
-      <c r="H88" t="inlineStr">
-        <is>
-          <t>4.30%</t>
-        </is>
-      </c>
-      <c r="I88" t="inlineStr">
-        <is>
-          <t>-0.07%</t>
-        </is>
-      </c>
-      <c r="J88" t="n">
-        <v>80000</v>
-      </c>
-      <c r="K88" t="n">
-        <v>82000</v>
-      </c>
-      <c r="L88" t="inlineStr">
-        <is>
-          <t>2,000</t>
-        </is>
-      </c>
-      <c r="M88" t="inlineStr">
-        <is>
-          <t>2026-09-27_00993A_full_holdings.xlsx</t>
-        </is>
-      </c>
-    </row>
-    <row r="89">
-      <c r="A89" t="inlineStr">
-        <is>
-          <t>00993A</t>
-        </is>
-      </c>
-      <c r="B89" t="inlineStr">
-        <is>
-          <t>持續持有</t>
-        </is>
-      </c>
-      <c r="C89" t="inlineStr">
-        <is>
-          <t>加碼</t>
-        </is>
-      </c>
-      <c r="D89" t="inlineStr">
-        <is>
-          <t>6505</t>
-        </is>
-      </c>
-      <c r="E89" t="inlineStr">
-        <is>
-          <t>台塑石化</t>
-        </is>
-      </c>
-      <c r="F89" t="inlineStr">
-        <is>
-          <t>台塑化</t>
-        </is>
-      </c>
-      <c r="G89" t="inlineStr">
-        <is>
-          <t>0.29%</t>
-        </is>
-      </c>
-      <c r="H89" t="inlineStr">
-        <is>
-          <t>0.32%</t>
-        </is>
-      </c>
-      <c r="I89" t="inlineStr">
-        <is>
-          <t>+0.03%</t>
-        </is>
-      </c>
-      <c r="J89" t="n">
-        <v>339000</v>
-      </c>
-      <c r="K89" t="n">
-        <v>378000</v>
-      </c>
-      <c r="L89" t="inlineStr">
-        <is>
-          <t>39,000</t>
-        </is>
-      </c>
-      <c r="M89" t="inlineStr">
-        <is>
-          <t>2026-09-27_00993A_full_holdings.xlsx</t>
-        </is>
-      </c>
-    </row>
-    <row r="90">
-      <c r="A90" t="inlineStr">
-        <is>
-          <t>00993A</t>
-        </is>
-      </c>
-      <c r="B90" t="inlineStr">
-        <is>
-          <t>持續持有</t>
-        </is>
-      </c>
-      <c r="C90" t="inlineStr">
-        <is>
-          <t>加碼</t>
-        </is>
-      </c>
-      <c r="D90" t="inlineStr">
-        <is>
-          <t>8046</t>
-        </is>
-      </c>
-      <c r="E90" t="inlineStr">
-        <is>
-          <t>南電</t>
-        </is>
-      </c>
-      <c r="F90" t="inlineStr">
-        <is>
-          <t>南電</t>
-        </is>
-      </c>
-      <c r="G90" t="inlineStr">
-        <is>
-          <t>2.90%</t>
-        </is>
-      </c>
-      <c r="H90" t="inlineStr">
-        <is>
-          <t>3.05%</t>
-        </is>
-      </c>
-      <c r="I90" t="inlineStr">
-        <is>
-          <t>+0.15%</t>
-        </is>
-      </c>
-      <c r="J90" t="n">
-        <v>247000</v>
-      </c>
-      <c r="K90" t="n">
-        <v>254000</v>
-      </c>
-      <c r="L90" t="inlineStr">
-        <is>
-          <t>7,000</t>
-        </is>
-      </c>
-      <c r="M90" t="inlineStr">
-        <is>
-          <t>2026-09-27_00993A_full_holdings.xlsx</t>
-        </is>
-      </c>
-    </row>
-    <row r="91">
-      <c r="A91" t="inlineStr">
-        <is>
-          <t>00400A</t>
-        </is>
-      </c>
-      <c r="B91" t="inlineStr">
-        <is>
-          <t>持續持有</t>
-        </is>
-      </c>
-      <c r="C91" t="inlineStr">
-        <is>
-          <t>減碼</t>
-        </is>
-      </c>
-      <c r="D91" t="inlineStr">
-        <is>
-          <t>2454</t>
-        </is>
-      </c>
-      <c r="E91" t="inlineStr">
-        <is>
-          <t>聯發科</t>
-        </is>
-      </c>
-      <c r="F91" t="inlineStr">
-        <is>
-          <t>聯發科</t>
-        </is>
-      </c>
-      <c r="G91" t="inlineStr">
-        <is>
-          <t>7.99%</t>
-        </is>
-      </c>
-      <c r="H91" t="inlineStr">
-        <is>
-          <t>7.06%</t>
-        </is>
-      </c>
-      <c r="I91" t="inlineStr">
-        <is>
-          <t>-0.93%</t>
-        </is>
-      </c>
-      <c r="J91" t="n">
-        <v>442000</v>
-      </c>
-      <c r="K91" t="n">
-        <v>413000</v>
-      </c>
-      <c r="L91" t="inlineStr">
-        <is>
-          <t>-29,000</t>
-        </is>
-      </c>
-      <c r="M91" t="inlineStr">
-        <is>
-          <t>2026-09-27_00400A_full_holdings.xlsx</t>
-        </is>
-      </c>
-    </row>
-    <row r="92">
-      <c r="A92" t="inlineStr">
-        <is>
-          <t>00400A</t>
-        </is>
-      </c>
-      <c r="B92" t="inlineStr">
-        <is>
-          <t>持續持有</t>
-        </is>
-      </c>
-      <c r="C92" t="inlineStr">
-        <is>
-          <t>減碼</t>
-        </is>
-      </c>
-      <c r="D92" t="inlineStr">
-        <is>
-          <t>3443</t>
-        </is>
-      </c>
-      <c r="E92" t="inlineStr">
-        <is>
-          <t>創意</t>
-        </is>
-      </c>
-      <c r="F92" t="inlineStr">
-        <is>
-          <t>創意</t>
-        </is>
-      </c>
-      <c r="G92" t="inlineStr">
-        <is>
-          <t>5.04%</t>
-        </is>
-      </c>
-      <c r="H92" t="inlineStr">
-        <is>
-          <t>4.27%</t>
-        </is>
-      </c>
-      <c r="I92" t="inlineStr">
-        <is>
-          <t>-0.77%</t>
-        </is>
-      </c>
-      <c r="J92" t="n">
-        <v>173000</v>
-      </c>
-      <c r="K92" t="n">
-        <v>155000</v>
-      </c>
-      <c r="L92" t="inlineStr">
-        <is>
-          <t>-18,000</t>
-        </is>
-      </c>
-      <c r="M92" t="inlineStr">
-        <is>
-          <t>2026-09-27_00400A_full_holdings.xlsx</t>
-        </is>
-      </c>
-    </row>
-    <row r="93">
-      <c r="A93" t="inlineStr">
-        <is>
-          <t>00400A</t>
-        </is>
-      </c>
-      <c r="B93" t="inlineStr">
-        <is>
-          <t>持續持有</t>
-        </is>
-      </c>
-      <c r="C93" t="inlineStr">
-        <is>
-          <t>加碼</t>
-        </is>
-      </c>
-      <c r="D93" t="inlineStr">
-        <is>
-          <t>6505</t>
-        </is>
-      </c>
-      <c r="E93" t="inlineStr">
-        <is>
-          <t>台塑化</t>
-        </is>
-      </c>
-      <c r="F93" t="inlineStr">
-        <is>
-          <t>台塑化</t>
-        </is>
-      </c>
-      <c r="G93" t="inlineStr">
-        <is>
-          <t>1.46%</t>
-        </is>
-      </c>
-      <c r="H93" t="inlineStr">
-        <is>
-          <t>2.02%</t>
-        </is>
-      </c>
-      <c r="I93" t="inlineStr">
-        <is>
-          <t>+0.56%</t>
-        </is>
-      </c>
-      <c r="J93" t="n">
-        <v>4903000</v>
-      </c>
-      <c r="K93" t="n">
-        <v>6147000</v>
-      </c>
-      <c r="L93" t="inlineStr">
-        <is>
-          <t>1,244,000</t>
-        </is>
-      </c>
-      <c r="M93" t="inlineStr">
         <is>
           <t>2026-09-27_00400A_full_holdings.xlsx</t>
         </is>

--- a/etf_holdings/2026-09-29_daily_changes_changed_only.xlsx
+++ b/etf_holdings/2026-09-29_daily_changes_changed_only.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M69"/>
+  <dimension ref="A1:M81"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1494,7 +1494,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>00403A</t>
+          <t>00982A</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1509,55 +1509,55 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>2345</t>
+          <t>2059</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>智邦</t>
+          <t>川湖</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>智邦</t>
+          <t>川湖</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>2.42%</t>
+          <t>4.39%</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>2.24%</t>
+          <t>4.37%</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>-0.18%</t>
+          <t>-0.02%</t>
         </is>
       </c>
       <c r="J18" t="n">
-        <v>1900000</v>
+        <v>180000</v>
       </c>
       <c r="K18" t="n">
-        <v>1800000</v>
+        <v>179000</v>
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>-100,000</t>
+          <t>-1,000</t>
         </is>
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>2026-09-27_00403A_full_holdings.xlsx</t>
+          <t>2026-09-27_00982A_full_holdings.xlsx</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>00403A</t>
+          <t>00982A</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1572,55 +1572,55 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>2360</t>
+          <t>2301</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>致茂</t>
+          <t>光寶科</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>致茂</t>
+          <t>光寶科</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>0.48%</t>
+          <t>1.80%</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>0.21%</t>
+          <t>1.82%</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>-0.27%</t>
+          <t>+0.02%</t>
         </is>
       </c>
       <c r="J19" t="n">
-        <v>310000</v>
+        <v>3230000</v>
       </c>
       <c r="K19" t="n">
-        <v>140000</v>
+        <v>3216000</v>
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>-170,000</t>
+          <t>-14,000</t>
         </is>
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>2026-09-27_00403A_full_holdings.xlsx</t>
+          <t>2026-09-27_00982A_full_holdings.xlsx</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>00403A</t>
+          <t>00982A</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1635,55 +1635,55 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>3017</t>
+          <t>2303</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>奇鋐</t>
+          <t>聯電</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>奇鋐</t>
+          <t>聯電</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>6.81%</t>
+          <t>1.62%</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>5.84%</t>
+          <t>1.56%</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>-0.97%</t>
+          <t>-0.06%</t>
         </is>
       </c>
       <c r="J20" t="n">
-        <v>2850000</v>
+        <v>5145000</v>
       </c>
       <c r="K20" t="n">
-        <v>2500000</v>
+        <v>5116000</v>
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>-350,000</t>
+          <t>-29,000</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>2026-09-27_00403A_full_holdings.xlsx</t>
+          <t>2026-09-27_00982A_full_holdings.xlsx</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>00403A</t>
+          <t>00982A</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -1698,55 +1698,55 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>3443</t>
+          <t>2345</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>創意</t>
+          <t>智邦</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>創意</t>
+          <t>智邦</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>3.70%</t>
+          <t>2.31%</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>3.32%</t>
+          <t>2.02%</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>-0.38%</t>
+          <t>-0.29%</t>
         </is>
       </c>
       <c r="J21" t="n">
-        <v>646000</v>
+        <v>621000</v>
       </c>
       <c r="K21" t="n">
-        <v>610000</v>
+        <v>541000</v>
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>-36,000</t>
+          <t>-80,000</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>2026-09-27_00403A_full_holdings.xlsx</t>
+          <t>2026-09-27_00982A_full_holdings.xlsx</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>00403A</t>
+          <t>00982A</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -1756,330 +1756,438 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>加碼</t>
+          <t>減碼</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>8996</t>
+          <t>2360</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>高力</t>
+          <t>致茂</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>高力</t>
+          <t>致茂</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>1.67%</t>
+          <t>3.75%</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>1.85%</t>
+          <t>3.69%</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>+0.18%</t>
+          <t>-0.06%</t>
         </is>
       </c>
       <c r="J22" t="n">
-        <v>1625000</v>
+        <v>820000</v>
       </c>
       <c r="K22" t="n">
-        <v>1700000</v>
+        <v>815000</v>
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>75,000</t>
+          <t>-5,000</t>
         </is>
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>2026-09-27_00403A_full_holdings.xlsx</t>
+          <t>2026-09-27_00982A_full_holdings.xlsx</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>00985A</t>
+          <t>00982A</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>新增</t>
+          <t>持續持有</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>新納入</t>
+          <t>減碼</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>3324</t>
-        </is>
-      </c>
-      <c r="E23" t="inlineStr"/>
+          <t>2376</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>技嘉</t>
+        </is>
+      </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>雙鴻</t>
-        </is>
-      </c>
-      <c r="G23" t="inlineStr"/>
+          <t>技嘉</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>1.26%</t>
+        </is>
+      </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>0.29%</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr"/>
-      <c r="J23" t="inlineStr"/>
+          <t>1.24%</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>-0.02%</t>
+        </is>
+      </c>
+      <c r="J23" t="n">
+        <v>1749000</v>
+      </c>
       <c r="K23" t="n">
-        <v>18000</v>
-      </c>
-      <c r="L23" t="inlineStr"/>
+        <v>1737000</v>
+      </c>
+      <c r="L23" t="inlineStr">
+        <is>
+          <t>-12,000</t>
+        </is>
+      </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>2026-09-27_00985A_full_holdings.xlsx</t>
+          <t>2026-09-27_00982A_full_holdings.xlsx</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>00985A</t>
+          <t>00982A</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>新增</t>
+          <t>持續持有</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>新納入</t>
+          <t>減碼</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>6526</t>
-        </is>
-      </c>
-      <c r="E24" t="inlineStr"/>
+          <t>2377</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>微星</t>
+        </is>
+      </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>達發</t>
-        </is>
-      </c>
-      <c r="G24" t="inlineStr"/>
+          <t>微星</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>1.00%</t>
+        </is>
+      </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>0.80%</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr"/>
-      <c r="J24" t="inlineStr"/>
+          <t>1.00%</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>0.00%</t>
+        </is>
+      </c>
+      <c r="J24" t="n">
+        <v>3372000</v>
+      </c>
       <c r="K24" t="n">
-        <v>102000</v>
-      </c>
-      <c r="L24" t="inlineStr"/>
+        <v>3344000</v>
+      </c>
+      <c r="L24" t="inlineStr">
+        <is>
+          <t>-28,000</t>
+        </is>
+      </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>2026-09-27_00985A_full_holdings.xlsx</t>
+          <t>2026-09-27_00982A_full_holdings.xlsx</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>00985A</t>
+          <t>00982A</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>新增</t>
+          <t>持續持有</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>新納入</t>
+          <t>減碼</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>6531</t>
-        </is>
-      </c>
-      <c r="E25" t="inlineStr"/>
+          <t>2383</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>台光電</t>
+        </is>
+      </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>愛普*</t>
-        </is>
-      </c>
-      <c r="G25" t="inlineStr"/>
+          <t>台光電</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>3.07%</t>
+        </is>
+      </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>0.71%</t>
-        </is>
-      </c>
-      <c r="I25" t="inlineStr"/>
-      <c r="J25" t="inlineStr"/>
+          <t>3.08%</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>+0.01%</t>
+        </is>
+      </c>
+      <c r="J25" t="n">
+        <v>311000</v>
+      </c>
       <c r="K25" t="n">
-        <v>76000</v>
-      </c>
-      <c r="L25" t="inlineStr"/>
+        <v>309000</v>
+      </c>
+      <c r="L25" t="inlineStr">
+        <is>
+          <t>-2,000</t>
+        </is>
+      </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>2026-09-27_00985A_full_holdings.xlsx</t>
+          <t>2026-09-27_00982A_full_holdings.xlsx</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>00985A</t>
+          <t>00982A</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>刪除</t>
+          <t>持續持有</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>全數賣出</t>
+          <t>減碼</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>2891</t>
+          <t>2395</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>中國信託金融控股</t>
-        </is>
-      </c>
-      <c r="F26" t="inlineStr"/>
+          <t>研華</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>研華</t>
+        </is>
+      </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>0.19%</t>
-        </is>
-      </c>
-      <c r="H26" t="inlineStr"/>
-      <c r="I26" t="inlineStr"/>
+          <t>1.56%</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>1.37%</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>-0.19%</t>
+        </is>
+      </c>
       <c r="J26" t="n">
-        <v>297000</v>
-      </c>
-      <c r="K26" t="inlineStr"/>
-      <c r="L26" t="inlineStr"/>
+        <v>1128000</v>
+      </c>
+      <c r="K26" t="n">
+        <v>964000</v>
+      </c>
+      <c r="L26" t="inlineStr">
+        <is>
+          <t>-164,000</t>
+        </is>
+      </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>2026-09-27_00985A_full_holdings.xlsx</t>
+          <t>2026-09-27_00982A_full_holdings.xlsx</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>00985A</t>
+          <t>00982A</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>刪除</t>
+          <t>持續持有</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>全數賣出</t>
+          <t>減碼</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>3036</t>
+          <t>2428</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>文曄科技</t>
-        </is>
-      </c>
-      <c r="F27" t="inlineStr"/>
+          <t>興勤</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>興勤</t>
+        </is>
+      </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="H27" t="inlineStr"/>
-      <c r="I27" t="inlineStr"/>
+          <t>1.14%</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>1.14%</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>0.00%</t>
+        </is>
+      </c>
       <c r="J27" t="n">
-        <v>1000</v>
-      </c>
-      <c r="K27" t="inlineStr"/>
-      <c r="L27" t="inlineStr"/>
+        <v>2285000</v>
+      </c>
+      <c r="K27" t="n">
+        <v>2268000</v>
+      </c>
+      <c r="L27" t="inlineStr">
+        <is>
+          <t>-17,000</t>
+        </is>
+      </c>
       <c r="M27" t="inlineStr">
         <is>
-          <t>2026-09-27_00985A_full_holdings.xlsx</t>
+          <t>2026-09-27_00982A_full_holdings.xlsx</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>00985A</t>
+          <t>00982A</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>刪除</t>
+          <t>持續持有</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>全數賣出</t>
+          <t>減碼</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>8299</t>
+          <t>2455</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>群聯電子</t>
-        </is>
-      </c>
-      <c r="F28" t="inlineStr"/>
+          <t>全新</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>全新</t>
+        </is>
+      </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>0.02%</t>
-        </is>
-      </c>
-      <c r="H28" t="inlineStr"/>
-      <c r="I28" t="inlineStr"/>
+          <t>1.67%</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>1.67%</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>0.00%</t>
+        </is>
+      </c>
       <c r="J28" t="n">
-        <v>1000</v>
-      </c>
-      <c r="K28" t="inlineStr"/>
-      <c r="L28" t="inlineStr"/>
+        <v>1537000</v>
+      </c>
+      <c r="K28" t="n">
+        <v>1529000</v>
+      </c>
+      <c r="L28" t="inlineStr">
+        <is>
+          <t>-8,000</t>
+        </is>
+      </c>
       <c r="M28" t="inlineStr">
         <is>
-          <t>2026-09-27_00985A_full_holdings.xlsx</t>
+          <t>2026-09-27_00982A_full_holdings.xlsx</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>00985A</t>
+          <t>00982A</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -2094,55 +2202,55 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>1504</t>
+          <t>2478</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>東元電機</t>
+          <t>大毅</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>東元</t>
+          <t>大毅</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>1.86%</t>
+          <t>1.03%</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>1.40%</t>
+          <t>1.03%</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>-0.46%</t>
+          <t>0.00%</t>
         </is>
       </c>
       <c r="J29" t="n">
-        <v>2904000</v>
+        <v>4360000</v>
       </c>
       <c r="K29" t="n">
-        <v>2177000</v>
+        <v>4331000</v>
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>-727,000</t>
+          <t>-29,000</t>
         </is>
       </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t>2026-09-27_00985A_full_holdings.xlsx</t>
+          <t>2026-09-27_00982A_full_holdings.xlsx</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>00985A</t>
+          <t>00982A</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -2157,55 +2265,55 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>2317</t>
+          <t>3008</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>鴻海精密工業</t>
+          <t>大立光</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>鴻海</t>
+          <t>大立光</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>2.45%</t>
+          <t>3.07%</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>2.00%</t>
+          <t>3.10%</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>-0.45%</t>
+          <t>+0.03%</t>
         </is>
       </c>
       <c r="J30" t="n">
-        <v>1021000</v>
+        <v>252000</v>
       </c>
       <c r="K30" t="n">
-        <v>853000</v>
+        <v>251000</v>
       </c>
       <c r="L30" t="inlineStr">
         <is>
-          <t>-168,000</t>
+          <t>-1,000</t>
         </is>
       </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t>2026-09-27_00985A_full_holdings.xlsx</t>
+          <t>2026-09-27_00982A_full_holdings.xlsx</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>00985A</t>
+          <t>00982A</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -2220,55 +2328,55 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>2376</t>
+          <t>3090</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>技嘉科技</t>
+          <t>日電貿</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>技嘉</t>
+          <t>日電貿</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>4.17%</t>
+          <t>1.07%</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>3.49%</t>
+          <t>1.07%</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>-0.68%</t>
+          <t>0.00%</t>
         </is>
       </c>
       <c r="J31" t="n">
-        <v>1222000</v>
+        <v>3302000</v>
       </c>
       <c r="K31" t="n">
-        <v>1030000</v>
+        <v>3280000</v>
       </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t>-192,000</t>
+          <t>-22,000</t>
         </is>
       </c>
       <c r="M31" t="inlineStr">
         <is>
-          <t>2026-09-27_00985A_full_holdings.xlsx</t>
+          <t>2026-09-27_00982A_full_holdings.xlsx</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>00985A</t>
+          <t>00982A</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -2283,55 +2391,55 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>3189</t>
+          <t>3231</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>景碩科技</t>
+          <t>緯創</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>景碩</t>
+          <t>緯創</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>1.66%</t>
+          <t>1.30%</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>1.06%</t>
+          <t>1.33%</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>-0.60%</t>
+          <t>+0.03%</t>
         </is>
       </c>
       <c r="J32" t="n">
-        <v>196000</v>
+        <v>3660000</v>
       </c>
       <c r="K32" t="n">
-        <v>118000</v>
+        <v>3638000</v>
       </c>
       <c r="L32" t="inlineStr">
         <is>
-          <t>-78,000</t>
+          <t>-22,000</t>
         </is>
       </c>
       <c r="M32" t="inlineStr">
         <is>
-          <t>2026-09-27_00985A_full_holdings.xlsx</t>
+          <t>2026-09-27_00982A_full_holdings.xlsx</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>00985A</t>
+          <t>00982A</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -2346,55 +2454,55 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>8046</t>
+          <t>3265</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>南亞電路板</t>
+          <t>台星科</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>南電</t>
+          <t>台星科</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>2.17%</t>
+          <t>1.19%</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>1.49%</t>
+          <t>1.21%</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>-0.68%</t>
+          <t>+0.02%</t>
         </is>
       </c>
       <c r="J33" t="n">
-        <v>192000</v>
+        <v>3369000</v>
       </c>
       <c r="K33" t="n">
-        <v>128000</v>
+        <v>3345000</v>
       </c>
       <c r="L33" t="inlineStr">
         <is>
-          <t>-64,000</t>
+          <t>-24,000</t>
         </is>
       </c>
       <c r="M33" t="inlineStr">
         <is>
-          <t>2026-09-27_00985A_full_holdings.xlsx</t>
+          <t>2026-09-27_00982A_full_holdings.xlsx</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>00985A</t>
+          <t>00982A</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -2409,55 +2517,55 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>8996</t>
+          <t>3711</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>高力熱處理工業</t>
+          <t>日月光投控</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>高力</t>
+          <t>日月光投控</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>1.10%</t>
+          <t>1.24%</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>0.79%</t>
+          <t>1.21%</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>-0.31%</t>
+          <t>-0.03%</t>
         </is>
       </c>
       <c r="J34" t="n">
-        <v>76000</v>
+        <v>906000</v>
       </c>
       <c r="K34" t="n">
-        <v>55000</v>
+        <v>876000</v>
       </c>
       <c r="L34" t="inlineStr">
         <is>
-          <t>-21,000</t>
+          <t>-30,000</t>
         </is>
       </c>
       <c r="M34" t="inlineStr">
         <is>
-          <t>2026-09-27_00985A_full_holdings.xlsx</t>
+          <t>2026-09-27_00982A_full_holdings.xlsx</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>00992A</t>
+          <t>00982A</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -2472,55 +2580,55 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>1303</t>
+          <t>5425</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>南亞</t>
+          <t>台半</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>南亞</t>
+          <t>台半</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>2.94%</t>
+          <t>1.21%</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>2.06%</t>
+          <t>1.19%</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>-0.88%</t>
+          <t>-0.02%</t>
         </is>
       </c>
       <c r="J35" t="n">
-        <v>5445000</v>
+        <v>6403000</v>
       </c>
       <c r="K35" t="n">
-        <v>3645000</v>
+        <v>6382000</v>
       </c>
       <c r="L35" t="inlineStr">
         <is>
-          <t>-1,800,000</t>
+          <t>-21,000</t>
         </is>
       </c>
       <c r="M35" t="inlineStr">
         <is>
-          <t>2026-09-27_00992A_full_holdings.xlsx</t>
+          <t>2026-09-27_00982A_full_holdings.xlsx</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>00993A</t>
+          <t>00982A</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -2530,60 +2638,60 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>加碼</t>
+          <t>減碼</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>1560</t>
+          <t>5483</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>中砂</t>
+          <t>中美晶</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>中砂</t>
+          <t>中美晶</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>0.86%</t>
+          <t>1.25%</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>1.00%</t>
+          <t>1.27%</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>+0.14%</t>
+          <t>+0.02%</t>
         </is>
       </c>
       <c r="J36" t="n">
-        <v>93000</v>
+        <v>3437000</v>
       </c>
       <c r="K36" t="n">
-        <v>106000</v>
+        <v>3415000</v>
       </c>
       <c r="L36" t="inlineStr">
         <is>
-          <t>13,000</t>
+          <t>-22,000</t>
         </is>
       </c>
       <c r="M36" t="inlineStr">
         <is>
-          <t>2026-09-27_00993A_full_holdings.xlsx</t>
+          <t>2026-09-27_00982A_full_holdings.xlsx</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>00993A</t>
+          <t>00982A</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -2593,60 +2701,60 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>加碼</t>
+          <t>減碼</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>2006</t>
+          <t>6139</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>東和鋼鐵</t>
+          <t>亞翔</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>東和鋼鐵</t>
+          <t>亞翔</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>0.52%</t>
+          <t>5.39%</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>0.59%</t>
+          <t>5.50%</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>+0.07%</t>
+          <t>+0.11%</t>
         </is>
       </c>
       <c r="J37" t="n">
-        <v>628000</v>
+        <v>3721000</v>
       </c>
       <c r="K37" t="n">
-        <v>699000</v>
+        <v>3697000</v>
       </c>
       <c r="L37" t="inlineStr">
         <is>
-          <t>71,000</t>
+          <t>-24,000</t>
         </is>
       </c>
       <c r="M37" t="inlineStr">
         <is>
-          <t>2026-09-27_00993A_full_holdings.xlsx</t>
+          <t>2026-09-27_00982A_full_holdings.xlsx</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>00993A</t>
+          <t>00982A</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -2656,60 +2764,60 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>加碼</t>
+          <t>減碼</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>2027</t>
+          <t>6214</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>大成鋼</t>
+          <t>精誠</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>大成鋼</t>
+          <t>精誠</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>0.19%</t>
+          <t>1.29%</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>0.21%</t>
+          <t>1.29%</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>+0.02%</t>
+          <t>0.00%</t>
         </is>
       </c>
       <c r="J38" t="n">
-        <v>416000</v>
+        <v>3460000</v>
       </c>
       <c r="K38" t="n">
-        <v>459000</v>
+        <v>3438000</v>
       </c>
       <c r="L38" t="inlineStr">
         <is>
-          <t>43,000</t>
+          <t>-22,000</t>
         </is>
       </c>
       <c r="M38" t="inlineStr">
         <is>
-          <t>2026-09-27_00993A_full_holdings.xlsx</t>
+          <t>2026-09-27_00982A_full_holdings.xlsx</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>00993A</t>
+          <t>00982A</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -2719,60 +2827,60 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>加碼</t>
+          <t>減碼</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>2301</t>
+          <t>6274</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>光寶科技</t>
+          <t>台燿</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>光寶科</t>
+          <t>台燿</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>0.22%</t>
+          <t>1.21%</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>0.25%</t>
+          <t>1.23%</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>+0.03%</t>
+          <t>+0.02%</t>
         </is>
       </c>
       <c r="J39" t="n">
-        <v>80000</v>
+        <v>421000</v>
       </c>
       <c r="K39" t="n">
-        <v>89000</v>
+        <v>418000</v>
       </c>
       <c r="L39" t="inlineStr">
         <is>
-          <t>9,000</t>
+          <t>-3,000</t>
         </is>
       </c>
       <c r="M39" t="inlineStr">
         <is>
-          <t>2026-09-27_00993A_full_holdings.xlsx</t>
+          <t>2026-09-27_00982A_full_holdings.xlsx</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>00993A</t>
+          <t>00982A</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -2782,60 +2890,60 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>加碼</t>
+          <t>減碼</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>2303</t>
+          <t>6488</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>聯電</t>
+          <t>環球晶</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>聯電</t>
+          <t>環球晶</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>2.85%</t>
+          <t>2.04%</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>2.89%</t>
+          <t>2.03%</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>+0.04%</t>
+          <t>-0.01%</t>
         </is>
       </c>
       <c r="J40" t="n">
-        <v>1835000</v>
+        <v>1089000</v>
       </c>
       <c r="K40" t="n">
-        <v>1938000</v>
+        <v>1082000</v>
       </c>
       <c r="L40" t="inlineStr">
         <is>
-          <t>103,000</t>
+          <t>-7,000</t>
         </is>
       </c>
       <c r="M40" t="inlineStr">
         <is>
-          <t>2026-09-27_00993A_full_holdings.xlsx</t>
+          <t>2026-09-27_00982A_full_holdings.xlsx</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>00993A</t>
+          <t>00982A</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -2845,60 +2953,60 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>加碼</t>
+          <t>減碼</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>2327</t>
+          <t>6672</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>國巨*</t>
+          <t>騰輝電子-KY</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>國巨*</t>
+          <t>騰輝電子-KY</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>2.03%</t>
+          <t>0.32%</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>2.18%</t>
+          <t>0.35%</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>+0.15%</t>
+          <t>+0.03%</t>
         </is>
       </c>
       <c r="J41" t="n">
-        <v>365000</v>
+        <v>530000</v>
       </c>
       <c r="K41" t="n">
-        <v>388000</v>
+        <v>527000</v>
       </c>
       <c r="L41" t="inlineStr">
         <is>
-          <t>23,000</t>
+          <t>-3,000</t>
         </is>
       </c>
       <c r="M41" t="inlineStr">
         <is>
-          <t>2026-09-27_00993A_full_holdings.xlsx</t>
+          <t>2026-09-27_00982A_full_holdings.xlsx</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>00993A</t>
+          <t>00403A</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -2908,60 +3016,60 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>加碼</t>
+          <t>減碼</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>2330</t>
+          <t>2345</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>台積電</t>
+          <t>智邦</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>台積電</t>
+          <t>智邦</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>8.42%</t>
+          <t>2.42%</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>8.32%</t>
+          <t>2.24%</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>-0.10%</t>
+          <t>-0.18%</t>
         </is>
       </c>
       <c r="J42" t="n">
-        <v>347000</v>
+        <v>1900000</v>
       </c>
       <c r="K42" t="n">
-        <v>349000</v>
+        <v>1800000</v>
       </c>
       <c r="L42" t="inlineStr">
         <is>
-          <t>2,000</t>
+          <t>-100,000</t>
         </is>
       </c>
       <c r="M42" t="inlineStr">
         <is>
-          <t>2026-09-27_00993A_full_holdings.xlsx</t>
+          <t>2026-09-27_00403A_full_holdings.xlsx</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>00993A</t>
+          <t>00403A</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -2971,60 +3079,60 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>加碼</t>
+          <t>減碼</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>2344</t>
+          <t>2360</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>華邦電子</t>
+          <t>致茂</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>華邦電</t>
+          <t>致茂</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>2.06%</t>
+          <t>0.48%</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>2.06%</t>
+          <t>0.21%</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>0.00%</t>
+          <t>-0.27%</t>
         </is>
       </c>
       <c r="J43" t="n">
-        <v>1228000</v>
+        <v>310000</v>
       </c>
       <c r="K43" t="n">
-        <v>1238000</v>
+        <v>140000</v>
       </c>
       <c r="L43" t="inlineStr">
         <is>
-          <t>10,000</t>
+          <t>-170,000</t>
         </is>
       </c>
       <c r="M43" t="inlineStr">
         <is>
-          <t>2026-09-27_00993A_full_holdings.xlsx</t>
+          <t>2026-09-27_00403A_full_holdings.xlsx</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>00993A</t>
+          <t>00403A</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -3034,60 +3142,60 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>加碼</t>
+          <t>減碼</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>2347</t>
+          <t>3017</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>聯強</t>
+          <t>奇鋐</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>聯強</t>
+          <t>奇鋐</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>0.43%</t>
+          <t>6.81%</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>0.43%</t>
+          <t>5.84%</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>0.00%</t>
+          <t>-0.97%</t>
         </is>
       </c>
       <c r="J44" t="n">
-        <v>465000</v>
+        <v>2850000</v>
       </c>
       <c r="K44" t="n">
-        <v>474000</v>
+        <v>2500000</v>
       </c>
       <c r="L44" t="inlineStr">
         <is>
-          <t>9,000</t>
+          <t>-350,000</t>
         </is>
       </c>
       <c r="M44" t="inlineStr">
         <is>
-          <t>2026-09-27_00993A_full_holdings.xlsx</t>
+          <t>2026-09-27_00403A_full_holdings.xlsx</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>00993A</t>
+          <t>00403A</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -3097,60 +3205,60 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>加碼</t>
+          <t>減碼</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>2360</t>
+          <t>3443</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>致茂</t>
+          <t>創意</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>致茂</t>
+          <t>創意</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>0.32%</t>
+          <t>3.70%</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>0.33%</t>
+          <t>3.32%</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>+0.01%</t>
+          <t>-0.38%</t>
         </is>
       </c>
       <c r="J45" t="n">
-        <v>14000</v>
+        <v>646000</v>
       </c>
       <c r="K45" t="n">
-        <v>15000</v>
+        <v>610000</v>
       </c>
       <c r="L45" t="inlineStr">
         <is>
-          <t>1,000</t>
+          <t>-36,000</t>
         </is>
       </c>
       <c r="M45" t="inlineStr">
         <is>
-          <t>2026-09-27_00993A_full_holdings.xlsx</t>
+          <t>2026-09-27_00403A_full_holdings.xlsx</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>00993A</t>
+          <t>00403A</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -3165,55 +3273,55 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>2383</t>
+          <t>8996</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>台光電子</t>
+          <t>高力</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>台光電</t>
+          <t>高力</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>4.88%</t>
+          <t>1.67%</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>4.94%</t>
+          <t>1.85%</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>+0.06%</t>
+          <t>+0.18%</t>
         </is>
       </c>
       <c r="J46" t="n">
-        <v>100000</v>
+        <v>1625000</v>
       </c>
       <c r="K46" t="n">
-        <v>101000</v>
+        <v>1700000</v>
       </c>
       <c r="L46" t="inlineStr">
         <is>
-          <t>1,000</t>
+          <t>75,000</t>
         </is>
       </c>
       <c r="M46" t="inlineStr">
         <is>
-          <t>2026-09-27_00993A_full_holdings.xlsx</t>
+          <t>2026-09-27_00403A_full_holdings.xlsx</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>00993A</t>
+          <t>00992A</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -3223,53 +3331,53 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>加碼</t>
+          <t>減碼</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>2395</t>
+          <t>1303</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>研華</t>
+          <t>南亞</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>研華</t>
+          <t>南亞</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>0.52%</t>
+          <t>2.94%</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>0.59%</t>
+          <t>2.06%</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>+0.07%</t>
+          <t>-0.88%</t>
         </is>
       </c>
       <c r="J47" t="n">
-        <v>76000</v>
+        <v>5445000</v>
       </c>
       <c r="K47" t="n">
-        <v>84000</v>
+        <v>3645000</v>
       </c>
       <c r="L47" t="inlineStr">
         <is>
-          <t>8,000</t>
+          <t>-1,800,000</t>
         </is>
       </c>
       <c r="M47" t="inlineStr">
         <is>
-          <t>2026-09-27_00993A_full_holdings.xlsx</t>
+          <t>2026-09-27_00992A_full_holdings.xlsx</t>
         </is>
       </c>
     </row>
@@ -3291,43 +3399,43 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>2408</t>
+          <t>1560</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>南亞科</t>
+          <t>中砂</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>南亞科</t>
+          <t>中砂</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>3.07%</t>
+          <t>0.86%</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>3.07%</t>
+          <t>1.00%</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>0.00%</t>
+          <t>+0.14%</t>
         </is>
       </c>
       <c r="J48" t="n">
-        <v>613000</v>
+        <v>93000</v>
       </c>
       <c r="K48" t="n">
-        <v>630000</v>
+        <v>106000</v>
       </c>
       <c r="L48" t="inlineStr">
         <is>
-          <t>17,000</t>
+          <t>13,000</t>
         </is>
       </c>
       <c r="M48" t="inlineStr">
@@ -3354,43 +3462,43 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>2412</t>
+          <t>2006</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>中華電</t>
+          <t>東和鋼鐵</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>中華電</t>
+          <t>東和鋼鐵</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>0.45%</t>
+          <t>0.52%</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>0.50%</t>
+          <t>0.59%</t>
         </is>
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>+0.05%</t>
+          <t>+0.07%</t>
         </is>
       </c>
       <c r="J49" t="n">
-        <v>319000</v>
+        <v>628000</v>
       </c>
       <c r="K49" t="n">
-        <v>357000</v>
+        <v>699000</v>
       </c>
       <c r="L49" t="inlineStr">
         <is>
-          <t>38,000</t>
+          <t>71,000</t>
         </is>
       </c>
       <c r="M49" t="inlineStr">
@@ -3417,43 +3525,43 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>2603</t>
+          <t>2027</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>長榮海運</t>
+          <t>大成鋼</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>長榮</t>
+          <t>大成鋼</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>0.29%</t>
+          <t>0.19%</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>0.32%</t>
+          <t>0.21%</t>
         </is>
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>+0.03%</t>
+          <t>+0.02%</t>
         </is>
       </c>
       <c r="J50" t="n">
-        <v>121000</v>
+        <v>416000</v>
       </c>
       <c r="K50" t="n">
-        <v>135000</v>
+        <v>459000</v>
       </c>
       <c r="L50" t="inlineStr">
         <is>
-          <t>14,000</t>
+          <t>43,000</t>
         </is>
       </c>
       <c r="M50" t="inlineStr">
@@ -3480,43 +3588,43 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>2606</t>
+          <t>2301</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>裕民</t>
+          <t>光寶科技</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>裕民</t>
+          <t>光寶科</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>0.33%</t>
+          <t>0.22%</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>0.37%</t>
+          <t>0.25%</t>
         </is>
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>+0.04%</t>
+          <t>+0.03%</t>
         </is>
       </c>
       <c r="J51" t="n">
-        <v>446000</v>
+        <v>80000</v>
       </c>
       <c r="K51" t="n">
-        <v>498000</v>
+        <v>89000</v>
       </c>
       <c r="L51" t="inlineStr">
         <is>
-          <t>52,000</t>
+          <t>9,000</t>
         </is>
       </c>
       <c r="M51" t="inlineStr">
@@ -3543,43 +3651,43 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>2618</t>
+          <t>2303</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>長榮航</t>
+          <t>聯電</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>長榮航</t>
+          <t>聯電</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>0.18%</t>
+          <t>2.85%</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>0.20%</t>
+          <t>2.89%</t>
         </is>
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t>+0.02%</t>
+          <t>+0.04%</t>
         </is>
       </c>
       <c r="J52" t="n">
-        <v>429000</v>
+        <v>1835000</v>
       </c>
       <c r="K52" t="n">
-        <v>487000</v>
+        <v>1938000</v>
       </c>
       <c r="L52" t="inlineStr">
         <is>
-          <t>58,000</t>
+          <t>103,000</t>
         </is>
       </c>
       <c r="M52" t="inlineStr">
@@ -3606,43 +3714,43 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>3017</t>
+          <t>2327</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>奇鋐</t>
+          <t>國巨*</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>奇鋐</t>
+          <t>國巨*</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>5.33%</t>
+          <t>2.03%</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>5.65%</t>
+          <t>2.18%</t>
         </is>
       </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t>+0.32%</t>
+          <t>+0.15%</t>
         </is>
       </c>
       <c r="J53" t="n">
-        <v>158000</v>
+        <v>365000</v>
       </c>
       <c r="K53" t="n">
-        <v>164000</v>
+        <v>388000</v>
       </c>
       <c r="L53" t="inlineStr">
         <is>
-          <t>6,000</t>
+          <t>23,000</t>
         </is>
       </c>
       <c r="M53" t="inlineStr">
@@ -3669,43 +3777,43 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>3037</t>
+          <t>2330</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>欣興</t>
+          <t>台積電</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>欣興</t>
+          <t>台積電</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>5.54%</t>
+          <t>8.42%</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>5.96%</t>
+          <t>8.32%</t>
         </is>
       </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t>+0.42%</t>
+          <t>-0.10%</t>
         </is>
       </c>
       <c r="J54" t="n">
-        <v>492000</v>
+        <v>347000</v>
       </c>
       <c r="K54" t="n">
-        <v>519000</v>
+        <v>349000</v>
       </c>
       <c r="L54" t="inlineStr">
         <is>
-          <t>27,000</t>
+          <t>2,000</t>
         </is>
       </c>
       <c r="M54" t="inlineStr">
@@ -3732,43 +3840,43 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>3189</t>
+          <t>2344</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>景碩科技</t>
+          <t>華邦電子</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>景碩</t>
+          <t>華邦電</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>3.77%</t>
+          <t>2.06%</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>4.01%</t>
+          <t>2.06%</t>
         </is>
       </c>
       <c r="I55" t="inlineStr">
         <is>
-          <t>+0.24%</t>
+          <t>0.00%</t>
         </is>
       </c>
       <c r="J55" t="n">
-        <v>428000</v>
+        <v>1228000</v>
       </c>
       <c r="K55" t="n">
-        <v>431000</v>
+        <v>1238000</v>
       </c>
       <c r="L55" t="inlineStr">
         <is>
-          <t>3,000</t>
+          <t>10,000</t>
         </is>
       </c>
       <c r="M55" t="inlineStr">
@@ -3795,43 +3903,43 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>3324</t>
+          <t>2347</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>雙鴻科技</t>
+          <t>聯強</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>雙鴻</t>
+          <t>聯強</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>0.54%</t>
+          <t>0.43%</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>0.63%</t>
+          <t>0.43%</t>
         </is>
       </c>
       <c r="I56" t="inlineStr">
         <is>
-          <t>+0.09%</t>
+          <t>0.00%</t>
         </is>
       </c>
       <c r="J56" t="n">
-        <v>35000</v>
+        <v>465000</v>
       </c>
       <c r="K56" t="n">
-        <v>38000</v>
+        <v>474000</v>
       </c>
       <c r="L56" t="inlineStr">
         <is>
-          <t>3,000</t>
+          <t>9,000</t>
         </is>
       </c>
       <c r="M56" t="inlineStr">
@@ -3858,43 +3966,43 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>3406</t>
+          <t>2360</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>玉晶光</t>
+          <t>致茂</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>玉晶光</t>
+          <t>致茂</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>0.25%</t>
+          <t>0.32%</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>0.29%</t>
+          <t>0.33%</t>
         </is>
       </c>
       <c r="I57" t="inlineStr">
         <is>
-          <t>+0.04%</t>
+          <t>+0.01%</t>
         </is>
       </c>
       <c r="J57" t="n">
-        <v>29000</v>
+        <v>14000</v>
       </c>
       <c r="K57" t="n">
-        <v>33000</v>
+        <v>15000</v>
       </c>
       <c r="L57" t="inlineStr">
         <is>
-          <t>4,000</t>
+          <t>1,000</t>
         </is>
       </c>
       <c r="M57" t="inlineStr">
@@ -3921,39 +4029,39 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>3443</t>
+          <t>2383</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>創意電子</t>
+          <t>台光電子</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>創意</t>
+          <t>台光電</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>5.29%</t>
+          <t>4.88%</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>5.45%</t>
+          <t>4.94%</t>
         </is>
       </c>
       <c r="I58" t="inlineStr">
         <is>
-          <t>+0.16%</t>
+          <t>+0.06%</t>
         </is>
       </c>
       <c r="J58" t="n">
-        <v>65000</v>
+        <v>100000</v>
       </c>
       <c r="K58" t="n">
-        <v>66000</v>
+        <v>101000</v>
       </c>
       <c r="L58" t="inlineStr">
         <is>
@@ -3984,43 +4092,43 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>3491</t>
+          <t>2395</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>昇達科技</t>
+          <t>研華</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>昇達科</t>
+          <t>研華</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>0.15%</t>
+          <t>0.52%</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>0.17%</t>
+          <t>0.59%</t>
         </is>
       </c>
       <c r="I59" t="inlineStr">
         <is>
-          <t>+0.02%</t>
+          <t>+0.07%</t>
         </is>
       </c>
       <c r="J59" t="n">
-        <v>10000</v>
+        <v>76000</v>
       </c>
       <c r="K59" t="n">
-        <v>11000</v>
+        <v>84000</v>
       </c>
       <c r="L59" t="inlineStr">
         <is>
-          <t>1,000</t>
+          <t>8,000</t>
         </is>
       </c>
       <c r="M59" t="inlineStr">
@@ -4047,43 +4155,43 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>3532</t>
+          <t>2408</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>台勝科</t>
+          <t>南亞科</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>台勝科</t>
+          <t>南亞科</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>0.30%</t>
+          <t>3.07%</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>0.35%</t>
+          <t>3.07%</t>
         </is>
       </c>
       <c r="I60" t="inlineStr">
         <is>
-          <t>+0.05%</t>
+          <t>0.00%</t>
         </is>
       </c>
       <c r="J60" t="n">
-        <v>70000</v>
+        <v>613000</v>
       </c>
       <c r="K60" t="n">
-        <v>80000</v>
+        <v>630000</v>
       </c>
       <c r="L60" t="inlineStr">
         <is>
-          <t>10,000</t>
+          <t>17,000</t>
         </is>
       </c>
       <c r="M60" t="inlineStr">
@@ -4110,43 +4218,43 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>3653</t>
+          <t>2412</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>健策</t>
+          <t>中華電</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>健策</t>
+          <t>中華電</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>1.37%</t>
+          <t>0.45%</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>2.28%</t>
+          <t>0.50%</t>
         </is>
       </c>
       <c r="I61" t="inlineStr">
         <is>
-          <t>+0.91%</t>
+          <t>+0.05%</t>
         </is>
       </c>
       <c r="J61" t="n">
-        <v>22000</v>
+        <v>319000</v>
       </c>
       <c r="K61" t="n">
-        <v>34000</v>
+        <v>357000</v>
       </c>
       <c r="L61" t="inlineStr">
         <is>
-          <t>12,000</t>
+          <t>38,000</t>
         </is>
       </c>
       <c r="M61" t="inlineStr">
@@ -4173,43 +4281,43 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>3711</t>
+          <t>2603</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>日月光投控</t>
+          <t>長榮海運</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>日月光投控</t>
+          <t>長榮</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>0.51%</t>
+          <t>0.29%</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>0.58%</t>
+          <t>0.32%</t>
         </is>
       </c>
       <c r="I62" t="inlineStr">
         <is>
-          <t>+0.07%</t>
+          <t>+0.03%</t>
         </is>
       </c>
       <c r="J62" t="n">
-        <v>76000</v>
+        <v>121000</v>
       </c>
       <c r="K62" t="n">
-        <v>85000</v>
+        <v>135000</v>
       </c>
       <c r="L62" t="inlineStr">
         <is>
-          <t>9,000</t>
+          <t>14,000</t>
         </is>
       </c>
       <c r="M62" t="inlineStr">
@@ -4236,43 +4344,43 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>4904</t>
+          <t>2606</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>遠傳</t>
+          <t>裕民</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>遠傳</t>
+          <t>裕民</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>0.24%</t>
+          <t>0.33%</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>0.27%</t>
+          <t>0.37%</t>
         </is>
       </c>
       <c r="I63" t="inlineStr">
         <is>
-          <t>+0.03%</t>
+          <t>+0.04%</t>
         </is>
       </c>
       <c r="J63" t="n">
-        <v>237000</v>
+        <v>446000</v>
       </c>
       <c r="K63" t="n">
-        <v>266000</v>
+        <v>498000</v>
       </c>
       <c r="L63" t="inlineStr">
         <is>
-          <t>29,000</t>
+          <t>52,000</t>
         </is>
       </c>
       <c r="M63" t="inlineStr">
@@ -4299,43 +4407,43 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>6223</t>
+          <t>2618</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>旺矽</t>
+          <t>長榮航</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>旺矽</t>
+          <t>長榮航</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>4.37%</t>
+          <t>0.18%</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>4.30%</t>
+          <t>0.20%</t>
         </is>
       </c>
       <c r="I64" t="inlineStr">
         <is>
-          <t>-0.07%</t>
+          <t>+0.02%</t>
         </is>
       </c>
       <c r="J64" t="n">
-        <v>80000</v>
+        <v>429000</v>
       </c>
       <c r="K64" t="n">
-        <v>82000</v>
+        <v>487000</v>
       </c>
       <c r="L64" t="inlineStr">
         <is>
-          <t>2,000</t>
+          <t>58,000</t>
         </is>
       </c>
       <c r="M64" t="inlineStr">
@@ -4362,43 +4470,43 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>6505</t>
+          <t>3017</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>台塑石化</t>
+          <t>奇鋐</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>台塑化</t>
+          <t>奇鋐</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>0.29%</t>
+          <t>5.33%</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>0.32%</t>
+          <t>5.65%</t>
         </is>
       </c>
       <c r="I65" t="inlineStr">
         <is>
-          <t>+0.03%</t>
+          <t>+0.32%</t>
         </is>
       </c>
       <c r="J65" t="n">
-        <v>339000</v>
+        <v>158000</v>
       </c>
       <c r="K65" t="n">
-        <v>378000</v>
+        <v>164000</v>
       </c>
       <c r="L65" t="inlineStr">
         <is>
-          <t>39,000</t>
+          <t>6,000</t>
         </is>
       </c>
       <c r="M65" t="inlineStr">
@@ -4425,43 +4533,43 @@
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>8046</t>
+          <t>3037</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>南電</t>
+          <t>欣興</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>南電</t>
+          <t>欣興</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>2.90%</t>
+          <t>5.54%</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>3.05%</t>
+          <t>5.96%</t>
         </is>
       </c>
       <c r="I66" t="inlineStr">
         <is>
-          <t>+0.15%</t>
+          <t>+0.42%</t>
         </is>
       </c>
       <c r="J66" t="n">
-        <v>247000</v>
+        <v>492000</v>
       </c>
       <c r="K66" t="n">
-        <v>254000</v>
+        <v>519000</v>
       </c>
       <c r="L66" t="inlineStr">
         <is>
-          <t>7,000</t>
+          <t>27,000</t>
         </is>
       </c>
       <c r="M66" t="inlineStr">
@@ -4473,7 +4581,7 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>00400A</t>
+          <t>00993A</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -4483,60 +4591,60 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>減碼</t>
+          <t>加碼</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>2454</t>
+          <t>3189</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>聯發科</t>
+          <t>景碩科技</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>聯發科</t>
+          <t>景碩</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>7.99%</t>
+          <t>3.77%</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>7.06%</t>
+          <t>4.01%</t>
         </is>
       </c>
       <c r="I67" t="inlineStr">
         <is>
-          <t>-0.93%</t>
+          <t>+0.24%</t>
         </is>
       </c>
       <c r="J67" t="n">
-        <v>442000</v>
+        <v>428000</v>
       </c>
       <c r="K67" t="n">
-        <v>413000</v>
+        <v>431000</v>
       </c>
       <c r="L67" t="inlineStr">
         <is>
-          <t>-29,000</t>
+          <t>3,000</t>
         </is>
       </c>
       <c r="M67" t="inlineStr">
         <is>
-          <t>2026-09-27_00400A_full_holdings.xlsx</t>
+          <t>2026-09-27_00993A_full_holdings.xlsx</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>00400A</t>
+          <t>00993A</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -4546,114 +4654,870 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>減碼</t>
+          <t>加碼</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>3443</t>
+          <t>3324</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>創意</t>
+          <t>雙鴻科技</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>創意</t>
+          <t>雙鴻</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>5.04%</t>
+          <t>0.54%</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>4.27%</t>
+          <t>0.63%</t>
         </is>
       </c>
       <c r="I68" t="inlineStr">
         <is>
-          <t>-0.77%</t>
+          <t>+0.09%</t>
         </is>
       </c>
       <c r="J68" t="n">
-        <v>173000</v>
+        <v>35000</v>
       </c>
       <c r="K68" t="n">
-        <v>155000</v>
+        <v>38000</v>
       </c>
       <c r="L68" t="inlineStr">
         <is>
-          <t>-18,000</t>
+          <t>3,000</t>
         </is>
       </c>
       <c r="M68" t="inlineStr">
         <is>
-          <t>2026-09-27_00400A_full_holdings.xlsx</t>
+          <t>2026-09-27_00993A_full_holdings.xlsx</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
+          <t>00993A</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>持續持有</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>加碼</t>
+        </is>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>3406</t>
+        </is>
+      </c>
+      <c r="E69" t="inlineStr">
+        <is>
+          <t>玉晶光</t>
+        </is>
+      </c>
+      <c r="F69" t="inlineStr">
+        <is>
+          <t>玉晶光</t>
+        </is>
+      </c>
+      <c r="G69" t="inlineStr">
+        <is>
+          <t>0.25%</t>
+        </is>
+      </c>
+      <c r="H69" t="inlineStr">
+        <is>
+          <t>0.29%</t>
+        </is>
+      </c>
+      <c r="I69" t="inlineStr">
+        <is>
+          <t>+0.04%</t>
+        </is>
+      </c>
+      <c r="J69" t="n">
+        <v>29000</v>
+      </c>
+      <c r="K69" t="n">
+        <v>33000</v>
+      </c>
+      <c r="L69" t="inlineStr">
+        <is>
+          <t>4,000</t>
+        </is>
+      </c>
+      <c r="M69" t="inlineStr">
+        <is>
+          <t>2026-09-27_00993A_full_holdings.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>00993A</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>持續持有</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>加碼</t>
+        </is>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>3443</t>
+        </is>
+      </c>
+      <c r="E70" t="inlineStr">
+        <is>
+          <t>創意電子</t>
+        </is>
+      </c>
+      <c r="F70" t="inlineStr">
+        <is>
+          <t>創意</t>
+        </is>
+      </c>
+      <c r="G70" t="inlineStr">
+        <is>
+          <t>5.29%</t>
+        </is>
+      </c>
+      <c r="H70" t="inlineStr">
+        <is>
+          <t>5.45%</t>
+        </is>
+      </c>
+      <c r="I70" t="inlineStr">
+        <is>
+          <t>+0.16%</t>
+        </is>
+      </c>
+      <c r="J70" t="n">
+        <v>65000</v>
+      </c>
+      <c r="K70" t="n">
+        <v>66000</v>
+      </c>
+      <c r="L70" t="inlineStr">
+        <is>
+          <t>1,000</t>
+        </is>
+      </c>
+      <c r="M70" t="inlineStr">
+        <is>
+          <t>2026-09-27_00993A_full_holdings.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>00993A</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>持續持有</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>加碼</t>
+        </is>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>3491</t>
+        </is>
+      </c>
+      <c r="E71" t="inlineStr">
+        <is>
+          <t>昇達科技</t>
+        </is>
+      </c>
+      <c r="F71" t="inlineStr">
+        <is>
+          <t>昇達科</t>
+        </is>
+      </c>
+      <c r="G71" t="inlineStr">
+        <is>
+          <t>0.15%</t>
+        </is>
+      </c>
+      <c r="H71" t="inlineStr">
+        <is>
+          <t>0.17%</t>
+        </is>
+      </c>
+      <c r="I71" t="inlineStr">
+        <is>
+          <t>+0.02%</t>
+        </is>
+      </c>
+      <c r="J71" t="n">
+        <v>10000</v>
+      </c>
+      <c r="K71" t="n">
+        <v>11000</v>
+      </c>
+      <c r="L71" t="inlineStr">
+        <is>
+          <t>1,000</t>
+        </is>
+      </c>
+      <c r="M71" t="inlineStr">
+        <is>
+          <t>2026-09-27_00993A_full_holdings.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>00993A</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>持續持有</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>加碼</t>
+        </is>
+      </c>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>3532</t>
+        </is>
+      </c>
+      <c r="E72" t="inlineStr">
+        <is>
+          <t>台勝科</t>
+        </is>
+      </c>
+      <c r="F72" t="inlineStr">
+        <is>
+          <t>台勝科</t>
+        </is>
+      </c>
+      <c r="G72" t="inlineStr">
+        <is>
+          <t>0.30%</t>
+        </is>
+      </c>
+      <c r="H72" t="inlineStr">
+        <is>
+          <t>0.35%</t>
+        </is>
+      </c>
+      <c r="I72" t="inlineStr">
+        <is>
+          <t>+0.05%</t>
+        </is>
+      </c>
+      <c r="J72" t="n">
+        <v>70000</v>
+      </c>
+      <c r="K72" t="n">
+        <v>80000</v>
+      </c>
+      <c r="L72" t="inlineStr">
+        <is>
+          <t>10,000</t>
+        </is>
+      </c>
+      <c r="M72" t="inlineStr">
+        <is>
+          <t>2026-09-27_00993A_full_holdings.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>00993A</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>持續持有</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>加碼</t>
+        </is>
+      </c>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>3653</t>
+        </is>
+      </c>
+      <c r="E73" t="inlineStr">
+        <is>
+          <t>健策</t>
+        </is>
+      </c>
+      <c r="F73" t="inlineStr">
+        <is>
+          <t>健策</t>
+        </is>
+      </c>
+      <c r="G73" t="inlineStr">
+        <is>
+          <t>1.37%</t>
+        </is>
+      </c>
+      <c r="H73" t="inlineStr">
+        <is>
+          <t>2.28%</t>
+        </is>
+      </c>
+      <c r="I73" t="inlineStr">
+        <is>
+          <t>+0.91%</t>
+        </is>
+      </c>
+      <c r="J73" t="n">
+        <v>22000</v>
+      </c>
+      <c r="K73" t="n">
+        <v>34000</v>
+      </c>
+      <c r="L73" t="inlineStr">
+        <is>
+          <t>12,000</t>
+        </is>
+      </c>
+      <c r="M73" t="inlineStr">
+        <is>
+          <t>2026-09-27_00993A_full_holdings.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>00993A</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>持續持有</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>加碼</t>
+        </is>
+      </c>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>3711</t>
+        </is>
+      </c>
+      <c r="E74" t="inlineStr">
+        <is>
+          <t>日月光投控</t>
+        </is>
+      </c>
+      <c r="F74" t="inlineStr">
+        <is>
+          <t>日月光投控</t>
+        </is>
+      </c>
+      <c r="G74" t="inlineStr">
+        <is>
+          <t>0.51%</t>
+        </is>
+      </c>
+      <c r="H74" t="inlineStr">
+        <is>
+          <t>0.58%</t>
+        </is>
+      </c>
+      <c r="I74" t="inlineStr">
+        <is>
+          <t>+0.07%</t>
+        </is>
+      </c>
+      <c r="J74" t="n">
+        <v>76000</v>
+      </c>
+      <c r="K74" t="n">
+        <v>85000</v>
+      </c>
+      <c r="L74" t="inlineStr">
+        <is>
+          <t>9,000</t>
+        </is>
+      </c>
+      <c r="M74" t="inlineStr">
+        <is>
+          <t>2026-09-27_00993A_full_holdings.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>00993A</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>持續持有</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>加碼</t>
+        </is>
+      </c>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>4904</t>
+        </is>
+      </c>
+      <c r="E75" t="inlineStr">
+        <is>
+          <t>遠傳</t>
+        </is>
+      </c>
+      <c r="F75" t="inlineStr">
+        <is>
+          <t>遠傳</t>
+        </is>
+      </c>
+      <c r="G75" t="inlineStr">
+        <is>
+          <t>0.24%</t>
+        </is>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>0.27%</t>
+        </is>
+      </c>
+      <c r="I75" t="inlineStr">
+        <is>
+          <t>+0.03%</t>
+        </is>
+      </c>
+      <c r="J75" t="n">
+        <v>237000</v>
+      </c>
+      <c r="K75" t="n">
+        <v>266000</v>
+      </c>
+      <c r="L75" t="inlineStr">
+        <is>
+          <t>29,000</t>
+        </is>
+      </c>
+      <c r="M75" t="inlineStr">
+        <is>
+          <t>2026-09-27_00993A_full_holdings.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>00993A</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>持續持有</t>
+        </is>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>加碼</t>
+        </is>
+      </c>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>6223</t>
+        </is>
+      </c>
+      <c r="E76" t="inlineStr">
+        <is>
+          <t>旺矽</t>
+        </is>
+      </c>
+      <c r="F76" t="inlineStr">
+        <is>
+          <t>旺矽</t>
+        </is>
+      </c>
+      <c r="G76" t="inlineStr">
+        <is>
+          <t>4.37%</t>
+        </is>
+      </c>
+      <c r="H76" t="inlineStr">
+        <is>
+          <t>4.30%</t>
+        </is>
+      </c>
+      <c r="I76" t="inlineStr">
+        <is>
+          <t>-0.07%</t>
+        </is>
+      </c>
+      <c r="J76" t="n">
+        <v>80000</v>
+      </c>
+      <c r="K76" t="n">
+        <v>82000</v>
+      </c>
+      <c r="L76" t="inlineStr">
+        <is>
+          <t>2,000</t>
+        </is>
+      </c>
+      <c r="M76" t="inlineStr">
+        <is>
+          <t>2026-09-27_00993A_full_holdings.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>00993A</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>持續持有</t>
+        </is>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>加碼</t>
+        </is>
+      </c>
+      <c r="D77" t="inlineStr">
+        <is>
+          <t>6505</t>
+        </is>
+      </c>
+      <c r="E77" t="inlineStr">
+        <is>
+          <t>台塑石化</t>
+        </is>
+      </c>
+      <c r="F77" t="inlineStr">
+        <is>
+          <t>台塑化</t>
+        </is>
+      </c>
+      <c r="G77" t="inlineStr">
+        <is>
+          <t>0.29%</t>
+        </is>
+      </c>
+      <c r="H77" t="inlineStr">
+        <is>
+          <t>0.32%</t>
+        </is>
+      </c>
+      <c r="I77" t="inlineStr">
+        <is>
+          <t>+0.03%</t>
+        </is>
+      </c>
+      <c r="J77" t="n">
+        <v>339000</v>
+      </c>
+      <c r="K77" t="n">
+        <v>378000</v>
+      </c>
+      <c r="L77" t="inlineStr">
+        <is>
+          <t>39,000</t>
+        </is>
+      </c>
+      <c r="M77" t="inlineStr">
+        <is>
+          <t>2026-09-27_00993A_full_holdings.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>00993A</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>持續持有</t>
+        </is>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>加碼</t>
+        </is>
+      </c>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t>8046</t>
+        </is>
+      </c>
+      <c r="E78" t="inlineStr">
+        <is>
+          <t>南電</t>
+        </is>
+      </c>
+      <c r="F78" t="inlineStr">
+        <is>
+          <t>南電</t>
+        </is>
+      </c>
+      <c r="G78" t="inlineStr">
+        <is>
+          <t>2.90%</t>
+        </is>
+      </c>
+      <c r="H78" t="inlineStr">
+        <is>
+          <t>3.05%</t>
+        </is>
+      </c>
+      <c r="I78" t="inlineStr">
+        <is>
+          <t>+0.15%</t>
+        </is>
+      </c>
+      <c r="J78" t="n">
+        <v>247000</v>
+      </c>
+      <c r="K78" t="n">
+        <v>254000</v>
+      </c>
+      <c r="L78" t="inlineStr">
+        <is>
+          <t>7,000</t>
+        </is>
+      </c>
+      <c r="M78" t="inlineStr">
+        <is>
+          <t>2026-09-27_00993A_full_holdings.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
           <t>00400A</t>
         </is>
       </c>
-      <c r="B69" t="inlineStr">
-        <is>
-          <t>持續持有</t>
-        </is>
-      </c>
-      <c r="C69" t="inlineStr">
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>持續持有</t>
+        </is>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>減碼</t>
+        </is>
+      </c>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t>2454</t>
+        </is>
+      </c>
+      <c r="E79" t="inlineStr">
+        <is>
+          <t>聯發科</t>
+        </is>
+      </c>
+      <c r="F79" t="inlineStr">
+        <is>
+          <t>聯發科</t>
+        </is>
+      </c>
+      <c r="G79" t="inlineStr">
+        <is>
+          <t>7.99%</t>
+        </is>
+      </c>
+      <c r="H79" t="inlineStr">
+        <is>
+          <t>7.06%</t>
+        </is>
+      </c>
+      <c r="I79" t="inlineStr">
+        <is>
+          <t>-0.93%</t>
+        </is>
+      </c>
+      <c r="J79" t="n">
+        <v>442000</v>
+      </c>
+      <c r="K79" t="n">
+        <v>413000</v>
+      </c>
+      <c r="L79" t="inlineStr">
+        <is>
+          <t>-29,000</t>
+        </is>
+      </c>
+      <c r="M79" t="inlineStr">
+        <is>
+          <t>2026-09-27_00400A_full_holdings.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>00400A</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>持續持有</t>
+        </is>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>減碼</t>
+        </is>
+      </c>
+      <c r="D80" t="inlineStr">
+        <is>
+          <t>3443</t>
+        </is>
+      </c>
+      <c r="E80" t="inlineStr">
+        <is>
+          <t>創意</t>
+        </is>
+      </c>
+      <c r="F80" t="inlineStr">
+        <is>
+          <t>創意</t>
+        </is>
+      </c>
+      <c r="G80" t="inlineStr">
+        <is>
+          <t>5.04%</t>
+        </is>
+      </c>
+      <c r="H80" t="inlineStr">
+        <is>
+          <t>4.27%</t>
+        </is>
+      </c>
+      <c r="I80" t="inlineStr">
+        <is>
+          <t>-0.77%</t>
+        </is>
+      </c>
+      <c r="J80" t="n">
+        <v>173000</v>
+      </c>
+      <c r="K80" t="n">
+        <v>155000</v>
+      </c>
+      <c r="L80" t="inlineStr">
+        <is>
+          <t>-18,000</t>
+        </is>
+      </c>
+      <c r="M80" t="inlineStr">
+        <is>
+          <t>2026-09-27_00400A_full_holdings.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>00400A</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>持續持有</t>
+        </is>
+      </c>
+      <c r="C81" t="inlineStr">
         <is>
           <t>加碼</t>
         </is>
       </c>
-      <c r="D69" t="inlineStr">
+      <c r="D81" t="inlineStr">
         <is>
           <t>6505</t>
         </is>
       </c>
-      <c r="E69" t="inlineStr">
+      <c r="E81" t="inlineStr">
         <is>
           <t>台塑化</t>
         </is>
       </c>
-      <c r="F69" t="inlineStr">
+      <c r="F81" t="inlineStr">
         <is>
           <t>台塑化</t>
         </is>
       </c>
-      <c r="G69" t="inlineStr">
+      <c r="G81" t="inlineStr">
         <is>
           <t>1.46%</t>
         </is>
       </c>
-      <c r="H69" t="inlineStr">
+      <c r="H81" t="inlineStr">
         <is>
           <t>2.02%</t>
         </is>
       </c>
-      <c r="I69" t="inlineStr">
+      <c r="I81" t="inlineStr">
         <is>
           <t>+0.56%</t>
         </is>
       </c>
-      <c r="J69" t="n">
+      <c r="J81" t="n">
         <v>4903000</v>
       </c>
-      <c r="K69" t="n">
+      <c r="K81" t="n">
         <v>6147000</v>
       </c>
-      <c r="L69" t="inlineStr">
+      <c r="L81" t="inlineStr">
         <is>
           <t>1,244,000</t>
         </is>
       </c>
-      <c r="M69" t="inlineStr">
+      <c r="M81" t="inlineStr">
         <is>
           <t>2026-09-27_00400A_full_holdings.xlsx</t>
         </is>
